--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P19" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.47</v>
+        <v>7.9</v>
       </c>
       <c r="O24" t="n">
-        <v>4.79</v>
+        <v>4.63</v>
       </c>
       <c r="P24" t="n">
-        <v>7.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>3.66</v>
+        <v>4.79</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>7.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>4.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7.9</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>4.63</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
-        <v>4.08</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>4.79</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O36" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O37" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P37" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O18" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P18" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>4.89</v>
+        <v>3.76</v>
       </c>
       <c r="P20" t="n">
-        <v>5.04</v>
+        <v>3.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>4.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.94</v>
+        <v>7.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3.39</v>
+        <v>4.63</v>
       </c>
       <c r="P30" t="n">
-        <v>4.32</v>
+        <v>1.43</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.49</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O35" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P35" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P36" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.56</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>3.68</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>3.56</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.14</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="O25" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>4.32</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>4.79</v>
+        <v>4.01</v>
       </c>
       <c r="P26" t="n">
-        <v>7.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>4.79</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>7.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>7.9</v>
       </c>
       <c r="O29" t="n">
-        <v>4.08</v>
+        <v>4.63</v>
       </c>
       <c r="P29" t="n">
-        <v>4.79</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>4.08</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>4.79</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P34" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P36" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O17" t="n">
-        <v>4.32</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>4.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O18" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P18" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.56</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>4.89</v>
+        <v>3.76</v>
       </c>
       <c r="P20" t="n">
-        <v>5.04</v>
+        <v>3.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="P25" t="n">
-        <v>4.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>4.01</v>
+        <v>4.79</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>7.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.79</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>7.12</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.9</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>4.63</v>
+        <v>4.08</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>4.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O34" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O36" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P36" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.56</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>4.68</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>3.56</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.14</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>7.9</v>
       </c>
       <c r="O25" t="n">
-        <v>3.36</v>
+        <v>4.63</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>4.79</v>
+        <v>3.36</v>
       </c>
       <c r="P26" t="n">
-        <v>7.12</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
-        <v>4.01</v>
+        <v>3.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>4.32</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>1.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>4.08</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>4.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>4.08</v>
+        <v>3.66</v>
       </c>
       <c r="P29" t="n">
-        <v>4.79</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.9</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>4.63</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.43</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O35" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P35" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O18" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P18" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51</v>
+        <v>4.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.47</v>
+        <v>7.9</v>
       </c>
       <c r="O24" t="n">
-        <v>4.79</v>
+        <v>4.63</v>
       </c>
       <c r="P24" t="n">
-        <v>7.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>7.9</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4.63</v>
+        <v>3.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>4.32</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>3.39</v>
+        <v>4.79</v>
       </c>
       <c r="P27" t="n">
-        <v>4.32</v>
+        <v>7.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5381,10 +5381,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O35" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P35" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O36" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P17" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>4.32</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>4.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.56</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7.9</v>
+        <v>2.35</v>
       </c>
       <c r="O24" t="n">
-        <v>4.63</v>
+        <v>3.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.94</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="P26" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P27" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>4.08</v>
+        <v>4.79</v>
       </c>
       <c r="P28" t="n">
-        <v>4.79</v>
+        <v>7.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="O31" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="P36" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51</v>
+        <v>4.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="O25" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
       <c r="P25" t="n">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.39</v>
+        <v>4.08</v>
       </c>
       <c r="P27" t="n">
-        <v>4.32</v>
+        <v>4.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.79</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>7.12</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.9</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>4.63</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.43</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P34" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O35" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P35" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P36" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>3.56</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="P19" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P20" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>7.9</v>
+        <v>1.73</v>
       </c>
       <c r="O25" t="n">
-        <v>4.63</v>
+        <v>4.08</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>4.79</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>4.79</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>7.12</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O34" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O36" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P16" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P17" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P20" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="O24" t="n">
-        <v>4.01</v>
+        <v>3.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>4.32</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P25" t="n">
-        <v>4.79</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.94</v>
+        <v>3.49</v>
       </c>
       <c r="O27" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="P27" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>4.79</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P34" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O35" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O16" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>3.56</v>
       </c>
       <c r="O17" t="n">
-        <v>4.89</v>
+        <v>4.14</v>
       </c>
       <c r="P17" t="n">
-        <v>5.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>4.51</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.94</v>
+        <v>7.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.39</v>
+        <v>4.63</v>
       </c>
       <c r="P24" t="n">
-        <v>4.32</v>
+        <v>1.43</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>7.9</v>
+        <v>1.94</v>
       </c>
       <c r="O26" t="n">
-        <v>4.63</v>
+        <v>3.39</v>
       </c>
       <c r="P26" t="n">
-        <v>1.43</v>
+        <v>4.32</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.49</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.66</v>
+        <v>4.08</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>4.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5222,10 +5222,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P35" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O36" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P36" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.56</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>5.04</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>4.32</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>4.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P21" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7.9</v>
+        <v>1.94</v>
       </c>
       <c r="O24" t="n">
-        <v>4.63</v>
+        <v>3.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.43</v>
+        <v>4.32</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.39</v>
+        <v>4.01</v>
       </c>
       <c r="P26" t="n">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.49</v>
+        <v>7.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>4.63</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O35" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P35" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>3.56</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="O24" t="n">
-        <v>3.39</v>
+        <v>4.08</v>
       </c>
       <c r="P24" t="n">
-        <v>4.32</v>
+        <v>4.79</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P26" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>7.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>4.63</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P29" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O30" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P30" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.9</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>4.63</v>
+        <v>3.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.43</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O35" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P35" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O36" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P36" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU37"/>
+  <dimension ref="A1:AU40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>8.24</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>5.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46225.66666666666</v>
+        <v>46225.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2109,27 +2109,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46225.77083333334</v>
+        <v>46225.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46225.8125</v>
+        <v>46225.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46225.8125</v>
+        <v>46225.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46225.8125</v>
+        <v>46225.77083333334</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46225.83333333334</v>
+        <v>46225.8125</v>
       </c>
     </row>
     <row r="16">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46225.85416666666</v>
+        <v>46225.8125</v>
       </c>
     </row>
     <row r="17">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46225.85416666666</v>
+        <v>46225.8125</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="O18" t="n">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>4.68</v>
+        <v>3.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46225.85416666666</v>
+        <v>46225.83333333334</v>
       </c>
     </row>
     <row r="19">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46225.875</v>
+        <v>46225.85416666666</v>
       </c>
     </row>
     <row r="23">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>4.08</v>
+        <v>4.32</v>
       </c>
       <c r="P23" t="n">
-        <v>4.94</v>
+        <v>4.68</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,17 +4103,17 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.63</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46225.88541666666</v>
+        <v>46225.85416666666</v>
       </c>
     </row>
     <row r="24">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.73</v>
+        <v>3.56</v>
       </c>
       <c r="O24" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="P24" t="n">
-        <v>4.79</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46225.89583333334</v>
+        <v>46225.85416666666</v>
       </c>
     </row>
     <row r="25">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46225.89583333334</v>
+        <v>46225.875</v>
       </c>
     </row>
     <row r="26">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.49</v>
+        <v>1.72</v>
       </c>
       <c r="O26" t="n">
-        <v>3.66</v>
+        <v>4.08</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>4.94</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46225.89583333334</v>
+        <v>46225.88541666666</v>
       </c>
     </row>
     <row r="27">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,14 +4700,14 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="P27" t="n">
         <v>4.79</v>
       </c>
-      <c r="P27" t="n">
-        <v>7.12</v>
-      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>7.9</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.63</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.48</v>
+        <v>7.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4.1</v>
+        <v>4.63</v>
       </c>
       <c r="P32" t="n">
-        <v>5.54</v>
+        <v>1.43</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46225.91666666666</v>
+        <v>46225.89583333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5699,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46225.9375</v>
+        <v>46225.89583333334</v>
       </c>
     </row>
     <row r="34">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>4.79</v>
       </c>
       <c r="P34" t="n">
-        <v>2.89</v>
+        <v>7.12</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46225.97916666666</v>
+        <v>46225.89583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O35" t="n">
-        <v>3.93</v>
+        <v>4.1</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>5.54</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46225.97916666666</v>
+        <v>46225.91666666666</v>
       </c>
     </row>
     <row r="36">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.76</v>
+        <v>2.17</v>
       </c>
       <c r="O36" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P36" t="n">
-        <v>4.47</v>
+        <v>3.16</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46225.97916666666</v>
+        <v>46225.9375</v>
       </c>
     </row>
     <row r="37">
@@ -6258,141 +6258,618 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>46225.97916666666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Orlando City</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>1.48</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O38" t="n">
         <v>5.2</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P38" t="n">
         <v>6.18</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AD38" t="n">
         <v>1.98</v>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" s="3" t="n">
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" s="3" t="n">
+        <v>46225.97916666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="3" t="n">
+        <v>46225.97916666666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" s="3" t="n">
         <v>46225.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51</v>
+        <v>4.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>3.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>3.56</v>
       </c>
       <c r="O22" t="n">
-        <v>4.89</v>
+        <v>4.14</v>
       </c>
       <c r="P22" t="n">
-        <v>5.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P23" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.56</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>3.68</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="O29" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.39</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5699,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O34" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P34" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O38" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P38" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P39" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>5.36</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.56</v>
+        <v>2.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>3.68</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O23" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.9</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>7.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>7.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.36</v>
+        <v>4.63</v>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5540,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O33" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P33" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>5.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P20" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O22" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P22" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>7.9</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>4.63</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>1.43</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O29" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P29" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P30" t="n">
-        <v>3.15</v>
+        <v>4.79</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.9</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
-        <v>4.63</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="P33" t="n">
-        <v>4.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5858,10 +5858,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O40" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P40" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>5.36</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.63</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O20" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P20" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.81</v>
+        <v>3.56</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="P23" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.9</v>
+        <v>3.49</v>
       </c>
       <c r="O27" t="n">
-        <v>4.63</v>
+        <v>3.66</v>
       </c>
       <c r="P27" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.94</v>
+        <v>7.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.39</v>
+        <v>4.63</v>
       </c>
       <c r="P29" t="n">
-        <v>4.32</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P30" t="n">
-        <v>4.79</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.49</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5540,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P33" t="n">
-        <v>3.15</v>
+        <v>4.79</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O40" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>3.65</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>5.36</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="O20" t="n">
-        <v>4.32</v>
+        <v>3.76</v>
       </c>
       <c r="P20" t="n">
-        <v>4.68</v>
+        <v>3.68</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O24" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.49</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.66</v>
+        <v>4.08</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>4.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>4.79</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>7.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="O33" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="P33" t="n">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>4.79</v>
+        <v>3.36</v>
       </c>
       <c r="P34" t="n">
-        <v>7.12</v>
+        <v>3.15</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P40" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6812,10 +6812,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>5.36</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O21" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.56</v>
+        <v>1.59</v>
       </c>
       <c r="O24" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>5.04</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>7.9</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>4.63</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>1.43</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7.9</v>
+        <v>1.73</v>
       </c>
       <c r="O32" t="n">
-        <v>4.63</v>
+        <v>4.08</v>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>4.79</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>3.39</v>
+        <v>4.01</v>
       </c>
       <c r="P33" t="n">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="P37" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>11.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,34 +2165,34 @@
         <v>3.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
         <v>2.2</v>
@@ -2201,19 +2201,19 @@
         <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,34 +2324,34 @@
         <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA12" t="n">
         <v>2.05</v>
@@ -2360,19 +2360,19 @@
         <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2801,34 +2801,34 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA15" t="n">
         <v>2.05</v>
@@ -2837,19 +2837,19 @@
         <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3278,55 +3278,55 @@
         <v>3.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>4.51</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.56</v>
+        <v>1.59</v>
       </c>
       <c r="O21" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>5.04</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O23" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P23" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O24" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>4.79</v>
+        <v>3.36</v>
       </c>
       <c r="P29" t="n">
-        <v>7.12</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.49</v>
+        <v>1.94</v>
       </c>
       <c r="O30" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>4.79</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>7.12</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.73</v>
+        <v>7.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4.08</v>
+        <v>4.63</v>
       </c>
       <c r="P32" t="n">
-        <v>4.79</v>
+        <v>1.43</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>4.79</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>3.49</v>
       </c>
       <c r="O34" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="P34" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB34" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5981,55 +5981,55 @@
         <v>5.54</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AE39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O40" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P40" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>8.24</v>
       </c>
       <c r="P9" t="n">
-        <v>5.36</v>
+        <v>11.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.07</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>3.24</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="O20" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="P20" t="n">
-        <v>3.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3914,40 +3914,40 @@
         <v>4.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
         <v>2.1</v>
@@ -3956,13 +3956,13 @@
         <v>1.63</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P24" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4550,34 +4550,34 @@
         <v>4.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="AA26" t="n">
         <v>1.63</v>
@@ -4586,19 +4586,19 @@
         <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>4.79</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.94</v>
+        <v>3.49</v>
       </c>
       <c r="O30" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="P30" t="n">
-        <v>4.32</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>4.07</v>
       </c>
       <c r="R30" t="n">
-        <v>1.99</v>
+        <v>2.43</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>7.9</v>
       </c>
       <c r="O31" t="n">
-        <v>4.79</v>
+        <v>4.63</v>
       </c>
       <c r="P31" t="n">
-        <v>7.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7.9</v>
+        <v>1.47</v>
       </c>
       <c r="O32" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>7.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>4.08</v>
+        <v>3.36</v>
       </c>
       <c r="P33" t="n">
-        <v>4.79</v>
+        <v>3.15</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="P34" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6140,40 +6140,40 @@
         <v>3.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC36" t="n">
         <v>2.1</v>
@@ -6182,13 +6182,13 @@
         <v>1.65</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O38" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P38" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6776,40 +6776,40 @@
         <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC40" t="n">
         <v>2.25</v>
@@ -6818,13 +6818,13 @@
         <v>1.57</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>5.36</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.07</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>3.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.56</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>4.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.89</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>5.04</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4.32</v>
+        <v>3.76</v>
       </c>
       <c r="P22" t="n">
-        <v>4.68</v>
+        <v>3.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.22</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>3.56</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>4.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.29</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,65 +5654,65 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3.36</v>
+        <v>4.08</v>
       </c>
       <c r="P33" t="n">
-        <v>3.15</v>
+        <v>4.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG33" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="O34" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="R34" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U34" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V37" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>6</v>
+        <v>5.06</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V38" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.13</v>
       </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z38" t="n">
-        <v>5.06</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="V39" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P40" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="S40" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T40" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="U40" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="V40" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="W40" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>3.65</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.2</v>
       </c>
-      <c r="O8" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>8.24</v>
       </c>
       <c r="P10" t="n">
-        <v>5.36</v>
+        <v>11.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="W10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.07</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>3.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.32</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>4.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="O21" t="n">
-        <v>4.89</v>
+        <v>3.76</v>
       </c>
       <c r="P21" t="n">
-        <v>5.04</v>
+        <v>3.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>3.76</v>
+        <v>4.32</v>
       </c>
       <c r="P22" t="n">
-        <v>3.68</v>
+        <v>4.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="S22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.25</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="AF22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>1.59</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>4.89</v>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>5.04</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="P27" t="n">
-        <v>4.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="O29" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="P29" t="n">
-        <v>3.15</v>
+        <v>4.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>7.9</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>4.63</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>7.9</v>
+        <v>1.47</v>
       </c>
       <c r="O31" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="P31" t="n">
-        <v>1.43</v>
+        <v>7.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>4.79</v>
+        <v>4.01</v>
       </c>
       <c r="P32" t="n">
-        <v>7.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.92</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK32" t="n">
-        <v>2.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,28 +6290,28 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="R37" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U37" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="V37" t="n">
         <v>1.6</v>
@@ -6323,16 +6323,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC37" t="n">
         <v>2.25</v>
@@ -6341,13 +6341,13 @@
         <v>1.57</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF37" t="n">
         <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="P38" t="n">
-        <v>2.89</v>
+        <v>4.47</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V38" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>5.06</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>5.2</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="R39" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T39" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="U39" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="V39" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O40" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="R40" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T40" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="V40" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.29</v>
       </c>
-      <c r="AB40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>5.36</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.07</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>3.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.24</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>4.51</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.89</v>
       </c>
       <c r="P20" t="n">
-        <v>4.51</v>
+        <v>5.04</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O22" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P22" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="R22" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="U22" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="O24" t="n">
-        <v>4.89</v>
+        <v>4.32</v>
       </c>
       <c r="P24" t="n">
-        <v>5.04</v>
+        <v>4.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="O27" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3.39</v>
+        <v>4.08</v>
       </c>
       <c r="P29" t="n">
-        <v>4.32</v>
+        <v>4.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="R29" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="S29" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O31" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P31" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="S31" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="T31" t="n">
-        <v>3.55</v>
+        <v>2.53</v>
       </c>
       <c r="U31" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,31 +5654,31 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>3.49</v>
       </c>
       <c r="O33" t="n">
-        <v>4.08</v>
+        <v>3.66</v>
       </c>
       <c r="P33" t="n">
-        <v>4.79</v>
+        <v>2.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.27</v>
+        <v>4.07</v>
       </c>
       <c r="R33" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S33" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T33" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U33" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W33" t="n">
         <v>1.11</v>
@@ -5687,31 +5687,31 @@
         <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.49</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
-        <v>3.66</v>
+        <v>4.79</v>
       </c>
       <c r="P34" t="n">
-        <v>2.12</v>
+        <v>7.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.07</v>
+        <v>1.92</v>
       </c>
       <c r="R34" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="S34" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T34" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U34" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="V34" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
         <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.29</v>
+        <v>2.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,28 +6290,28 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="R37" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="V37" t="n">
         <v>1.6</v>
@@ -6323,16 +6323,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AC37" t="n">
         <v>2.25</v>
@@ -6341,13 +6341,13 @@
         <v>1.57</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF37" t="n">
         <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>4.47</v>
+        <v>2.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V38" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.13</v>
       </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z38" t="n">
-        <v>5.06</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="V39" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG40" t="n">
         <v>2.75</v>
       </c>
-      <c r="R40" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB40" t="n">
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK40" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>3.65</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2960,34 +2960,34 @@
         <v>3.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA16" t="n">
         <v>1.97</v>
@@ -2996,19 +2996,19 @@
         <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>4.89</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>5.04</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O21" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P21" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.56</v>
+        <v>1.71</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>4.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="S22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.17</v>
       </c>
-      <c r="T22" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="O24" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="P24" t="n">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="U24" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>3.62</v>
+        <v>4.79</v>
       </c>
       <c r="P27" t="n">
-        <v>4.48</v>
+        <v>7.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,31 +5018,31 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>4.08</v>
+        <v>3.66</v>
       </c>
       <c r="P29" t="n">
-        <v>4.79</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.27</v>
+        <v>4.07</v>
       </c>
       <c r="R29" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S29" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W29" t="n">
         <v>1.11</v>
@@ -5051,31 +5051,31 @@
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.9</v>
+        <v>1.73</v>
       </c>
       <c r="O30" t="n">
-        <v>4.63</v>
+        <v>4.08</v>
       </c>
       <c r="P30" t="n">
-        <v>1.43</v>
+        <v>4.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3.39</v>
+        <v>4.01</v>
       </c>
       <c r="P31" t="n">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="S31" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="U31" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.49</v>
+        <v>7.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.66</v>
+        <v>4.63</v>
       </c>
       <c r="P33" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="O34" t="n">
-        <v>4.79</v>
+        <v>3.39</v>
       </c>
       <c r="P34" t="n">
-        <v>7.12</v>
+        <v>4.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="S34" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="T34" t="n">
-        <v>3.55</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X34" t="n">
         <v>1.03</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE34" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,28 +6290,28 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="R37" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T37" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U37" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="V37" t="n">
         <v>1.6</v>
@@ -6323,16 +6323,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC37" t="n">
         <v>2.25</v>
@@ -6341,13 +6341,13 @@
         <v>1.57</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF37" t="n">
         <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG38" t="n">
         <v>2.75</v>
       </c>
-      <c r="R38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="R39" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
         <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V39" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.13</v>
       </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="O40" t="n">
-        <v>5.2</v>
+        <v>4.21</v>
       </c>
       <c r="P40" t="n">
-        <v>6.18</v>
+        <v>4.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="R40" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="S40" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="U40" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="V40" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>5.06</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="P13" t="n">
         <v>2.95</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="U17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
         <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P19" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>3.56</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>4.14</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
-        <v>4.32</v>
+        <v>4.89</v>
       </c>
       <c r="P22" t="n">
-        <v>4.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>3.76</v>
+        <v>4.32</v>
       </c>
       <c r="P23" t="n">
-        <v>3.68</v>
+        <v>4.68</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="S23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.25</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AF23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="O27" t="n">
-        <v>4.79</v>
+        <v>3.62</v>
       </c>
       <c r="P27" t="n">
-        <v>7.12</v>
+        <v>4.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.62</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>4.48</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>7.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.66</v>
+        <v>4.63</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="O30" t="n">
-        <v>4.08</v>
+        <v>3.39</v>
       </c>
       <c r="P30" t="n">
-        <v>4.79</v>
+        <v>4.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="S30" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="T30" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="U30" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O31" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>4.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="R31" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="S31" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T31" t="n">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.15</v>
       </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>3.49</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="P32" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB32" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>7.9</v>
+        <v>1.47</v>
       </c>
       <c r="O33" t="n">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="P33" t="n">
-        <v>1.43</v>
+        <v>7.12</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.94</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>3.39</v>
+        <v>4.01</v>
       </c>
       <c r="P34" t="n">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="S34" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="T34" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.85</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.2</v>
       </c>
-      <c r="AE34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK34" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,28 +6290,28 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="R37" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="V37" t="n">
         <v>1.6</v>
@@ -6323,16 +6323,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AC37" t="n">
         <v>2.25</v>
@@ -6341,13 +6341,13 @@
         <v>1.57</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF37" t="n">
         <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P38" t="n">
-        <v>6.18</v>
+        <v>2.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="V38" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.29</v>
       </c>
-      <c r="AB38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.89</v>
+        <v>6.18</v>
       </c>
       <c r="Q39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG39" t="n">
         <v>2.75</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK39" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,28 +6767,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="O40" t="n">
-        <v>4.21</v>
+        <v>3.93</v>
       </c>
       <c r="P40" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="R40" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="S40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T40" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U40" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="V40" t="n">
         <v>1.6</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.06</v>
+        <v>5.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC40" t="n">
         <v>2.25</v>
@@ -6818,13 +6818,13 @@
         <v>1.57</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF40" t="n">
         <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>3.65</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>11.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="P10" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>3.88</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>4.62</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="U16" t="n">
-        <v>2.81</v>
+        <v>3.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.72</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.62</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
         <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
         <v>3.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
@@ -3302,31 +3302,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD18" t="n">
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.76</v>
+        <v>4.89</v>
       </c>
       <c r="P19" t="n">
-        <v>3.68</v>
+        <v>5.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.65</v>
+        <v>1.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.81</v>
+        <v>2.03</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="P21" t="n">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="O22" t="n">
-        <v>4.89</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>3.56</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>4.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3.62</v>
+        <v>4.08</v>
       </c>
       <c r="P27" t="n">
-        <v>4.48</v>
+        <v>4.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S27" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.88</v>
       </c>
-      <c r="U27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,31 +5336,31 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
-        <v>4.08</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>4.79</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.27</v>
+        <v>4.07</v>
       </c>
       <c r="R31" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S31" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T31" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U31" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W31" t="n">
         <v>1.11</v>
@@ -5369,31 +5369,31 @@
         <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.29</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>4.21</v>
+        <v>5.2</v>
       </c>
       <c r="P37" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>2.57</v>
+        <v>2.95</v>
       </c>
       <c r="S37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.06</v>
+        <v>8</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="O39" t="n">
-        <v>5.2</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>6.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T39" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="V39" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,28 +6767,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="O40" t="n">
-        <v>3.93</v>
+        <v>4.21</v>
       </c>
       <c r="P40" t="n">
-        <v>3.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U40" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="V40" t="n">
         <v>1.6</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AC40" t="n">
         <v>2.25</v>
@@ -6818,13 +6818,13 @@
         <v>1.57</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF40" t="n">
         <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.92</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>3.65</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>3.65</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>8.24</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>11.12</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="S8" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.78</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.26</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>1.18</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>5.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,34 +2156,34 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.13</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
@@ -2192,13 +2192,13 @@
         <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
         <v>4.1</v>
@@ -2210,10 +2210,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
         <v>1.72</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.43</v>
+        <v>3.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.62</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
         <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -3305,10 +3305,10 @@
         <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
         <v>2.02</v>
@@ -3320,13 +3320,13 @@
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
         <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.89</v>
+        <v>4.16</v>
       </c>
       <c r="P19" t="n">
-        <v>5.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.03</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.76</v>
+        <v>4.16</v>
       </c>
       <c r="P21" t="n">
-        <v>3.68</v>
+        <v>4.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.25</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>4.51</v>
+        <v>3.35</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
-        <v>4.32</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>4.68</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="R23" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T23" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.56</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>4.14</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>1.97</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4541,28 +4541,28 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>4.08</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>4.94</v>
+        <v>4.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V26" t="n">
         <v>1.51</v>
@@ -4571,28 +4571,28 @@
         <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
         <v>4.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
         <v>1.6</v>
@@ -4614,7 +4614,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P27" t="n">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.7</v>
+        <v>4.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O28" t="n">
-        <v>3.62</v>
+        <v>4.73</v>
       </c>
       <c r="P28" t="n">
-        <v>4.48</v>
+        <v>6.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="R28" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="S28" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="U28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK28" t="n">
         <v>2.8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>2.01</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,65 +5018,65 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.9</v>
+        <v>1.74</v>
       </c>
       <c r="O29" t="n">
-        <v>4.63</v>
+        <v>3.62</v>
       </c>
       <c r="P29" t="n">
-        <v>1.43</v>
+        <v>4.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.81</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="P30" t="n">
-        <v>4.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.49</v>
+        <v>1.82</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>3.87</v>
       </c>
       <c r="P31" t="n">
-        <v>2.12</v>
+        <v>4.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.07</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V31" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
         <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE31" t="n">
         <v>1.13</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S32" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T32" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.47</v>
       </c>
-      <c r="O33" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="P33" t="n">
-        <v>7.12</v>
-      </c>
       <c r="Q33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,25 +5972,25 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="P35" t="n">
-        <v>5.54</v>
+        <v>5.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R35" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S35" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
         <v>2.2</v>
@@ -5999,31 +5999,31 @@
         <v>1.59</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z35" t="n">
         <v>4.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
         <v>1.61</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK35" t="n">
         <v>2.5</v>
@@ -6131,19 +6131,19 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="O36" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="P36" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
         <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
         <v>1.2</v>
@@ -6155,40 +6155,40 @@
         <v>2.04</v>
       </c>
       <c r="V36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.7</v>
       </c>
-      <c r="W36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6293,28 +6293,28 @@
         <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="P37" t="n">
-        <v>6.18</v>
+        <v>5.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="S37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T37" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V37" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="W37" t="n">
         <v>1.25</v>
@@ -6326,19 +6326,19 @@
         <v>1.06</v>
       </c>
       <c r="Z37" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AE37" t="n">
         <v>1.4</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,31 +6449,31 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P38" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="R38" t="n">
         <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W38" t="n">
         <v>1.15</v>
@@ -6482,31 +6482,31 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z38" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>3.65</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="R39" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T39" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V39" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.1</v>
+        <v>5.83</v>
       </c>
       <c r="AA39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O40" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="R40" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
         <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U40" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V40" t="n">
         <v>1.6</v>
       </c>
       <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.13</v>
       </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z40" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF40" t="n">
         <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK40" t="n">
         <v>2.05</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.88</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.26</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK9" t="n">
-        <v>4.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>1.18</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>4.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>4.16</v>
       </c>
       <c r="P22" t="n">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>4.01</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.22</v>
       </c>
-      <c r="T27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.35</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="P30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.82</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>4.47</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T31" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
         <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>3.66</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.7</v>
+        <v>1.82</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>1.47</v>
+        <v>4.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="O37" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="P37" t="n">
-        <v>5.5</v>
+        <v>3.44</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="R37" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.15</v>
       </c>
-      <c r="T37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,31 +6449,31 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="P38" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V38" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W38" t="n">
         <v>1.15</v>
@@ -6482,31 +6482,31 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.25</v>
+        <v>5.83</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK39" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>4.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.11</v>
+        <v>7.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.01</v>
+        <v>1.26</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.74</v>
+        <v>3.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>1.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.1</v>
+        <v>4.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.18</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.88</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.26</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK10" t="n">
-        <v>4.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
-        <v>4.16</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.89</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,14 +3587,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="O20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P20" t="n">
         <v>3.1</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.16</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>4.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>4.16</v>
       </c>
       <c r="P22" t="n">
-        <v>4.32</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>3.98</v>
       </c>
       <c r="R22" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>6.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>2.05</v>
       </c>
-      <c r="S27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.41</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4.73</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>6.5</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="V28" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.45</v>
+        <v>4.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.74</v>
+        <v>6.7</v>
       </c>
       <c r="O29" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>4.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>4.01</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.22</v>
       </c>
-      <c r="T30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.49</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>3.87</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>4.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U31" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
         <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,65 +5495,65 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>1.41</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>4.73</v>
       </c>
       <c r="P32" t="n">
-        <v>3.15</v>
+        <v>6.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.82</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="P33" t="n">
-        <v>4.47</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T33" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
         <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK33" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>6.7</v>
+        <v>1.74</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>1.47</v>
+        <v>4.48</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
-        <v>3.84</v>
+        <v>5.1</v>
       </c>
       <c r="P37" t="n">
-        <v>3.44</v>
+        <v>5.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.45</v>
+        <v>3.42</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="O39" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="P39" t="n">
-        <v>5.5</v>
+        <v>3.44</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="R39" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.15</v>
       </c>
-      <c r="T39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="P4" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>1.09</v>
       </c>
       <c r="O8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB8" t="n">
         <v>4</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.18</v>
       </c>
-      <c r="O9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.65</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.98</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>2.01</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>3.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P15" t="n">
         <v>3.88</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.03</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4.69</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="U15" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>3.88</v>
       </c>
       <c r="O16" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.88</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>4.69</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="U16" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.77</v>
       </c>
-      <c r="AG16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.85</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>4.32</v>
+        <v>3.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
         <v>4.16</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.98</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S22" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="V22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.15</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,14 +4064,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="O23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P23" t="n">
         <v>3.1</v>
       </c>
-      <c r="P23" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="O27" t="n">
-        <v>3.36</v>
+        <v>3.87</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>4.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6.7</v>
+        <v>1.41</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="P29" t="n">
-        <v>1.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>4.47</v>
+        <v>3.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.33</v>
       </c>
-      <c r="T31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.41</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>4.73</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>4.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="S33" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T33" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.65</v>
+        <v>3.59</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.29</v>
+        <v>2.03</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="P34" t="n">
-        <v>4.48</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="S34" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.59</v>
+        <v>2.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.03</v>
+        <v>1.29</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="P37" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="R37" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="S37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.15</v>
       </c>
-      <c r="T37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.25</v>
       </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,16 +6608,16 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>3.44</v>
+        <v>4.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
         <v>2.4</v>
@@ -6626,46 +6626,46 @@
         <v>1.25</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V39" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF39" t="n">
         <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,16 +6767,16 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="O40" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P40" t="n">
-        <v>4.4</v>
+        <v>3.44</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="R40" t="n">
         <v>2.4</v>
@@ -6785,46 +6785,46 @@
         <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="U40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W40" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.17</v>
       </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF40" t="n">
         <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.09</v>
       </c>
-      <c r="O8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
         <v>2.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
         <v>1.12</v>
@@ -1874,7 +1874,7 @@
         <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.03</v>
+        <v>5.23</v>
       </c>
       <c r="AA9" t="n">
         <v>1.6</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.73</v>
+        <v>5.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.11</v>
+        <v>8.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.74</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>2.21</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O11" t="n">
         <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q11" t="n">
         <v>2.6</v>
@@ -2171,19 +2171,19 @@
         <v>2.11</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>3.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
@@ -2192,7 +2192,7 @@
         <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="AA11" t="n">
         <v>2.17</v>
@@ -2210,10 +2210,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
         <v>1.72</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="U12" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.01</v>
+        <v>3.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.88</v>
+        <v>3.33</v>
       </c>
       <c r="Q15" t="n">
         <v>2.7</v>
@@ -2807,49 +2807,49 @@
         <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.14</v>
+        <v>2.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
         <v>4.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>4.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.98</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.7</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.89</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.67</v>
       </c>
-      <c r="O22" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
         <v>2</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.63</v>
+        <v>3.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4541,40 +4541,40 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="P26" t="n">
         <v>4.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T26" t="n">
         <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
         <v>4.36</v>
@@ -4583,10 +4583,10 @@
         <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AD26" t="n">
         <v>1.47</v>
@@ -4598,7 +4598,7 @@
         <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.82</v>
+        <v>3.54</v>
       </c>
       <c r="O27" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="P27" t="n">
-        <v>4.47</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>4.07</v>
       </c>
       <c r="R27" t="n">
         <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
         <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4868,25 +4868,25 @@
         <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="R28" t="n">
         <v>2.45</v>
       </c>
       <c r="S28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T28" t="n">
         <v>3.6</v>
       </c>
       <c r="U28" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -4898,13 +4898,13 @@
         <v>4.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
         <v>2.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD28" t="n">
         <v>1.57</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.41</v>
       </c>
-      <c r="O29" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="P29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="T29" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="U29" t="n">
-        <v>2.38</v>
+        <v>3.02</v>
       </c>
       <c r="V29" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.45</v>
+        <v>3.08</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.52</v>
+        <v>3.61</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.2</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AK29" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.7</v>
+        <v>1.44</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>6.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P31" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.05</v>
       </c>
-      <c r="S31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>6.7</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>3.15</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R33" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T33" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U33" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.59</v>
+        <v>3.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
         <v>1.06</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="O34" t="n">
-        <v>3.66</v>
+        <v>3.87</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>4.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T34" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U34" t="n">
         <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W34" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
         <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6131,16 +6131,16 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="O36" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="P36" t="n">
         <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R36" t="n">
         <v>2.5</v>
@@ -6149,43 +6149,43 @@
         <v>1.2</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V36" t="n">
         <v>1.76</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB36" t="n">
         <v>2.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
         <v>2.84</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK36" t="n">
         <v>1.67</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>4.28</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U37" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="V37" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.15</v>
       </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z37" t="n">
-        <v>5.83</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
-        <v>5.1</v>
+        <v>3.93</v>
       </c>
       <c r="P38" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T38" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="V38" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="W38" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.5</v>
+        <v>5.28</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.42</v>
+        <v>2.45</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="P39" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.25</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.17</v>
       </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK39" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,31 +6767,31 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="P40" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S40" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T40" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U40" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V40" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W40" t="n">
         <v>1.15</v>
@@ -6800,31 +6800,31 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.25</v>
+        <v>5.83</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.88</v>
       </c>
-      <c r="S2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.39</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U4" t="n">
         <v>3.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.22</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>3.07</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.05</v>
+        <v>5.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.07</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>2.19</v>
+        <v>18</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.23</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.51</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S10" t="n">
         <v>1.39</v>
       </c>
-      <c r="R10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T10" t="n">
-        <v>5.15</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>2.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>5.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>3.94</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>3.33</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.7</v>
+        <v>4.76</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="S15" t="n">
         <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.04</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.88</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.69</v>
+        <v>2.52</v>
       </c>
       <c r="R16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.96</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3113,19 +3113,19 @@
         <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
         <v>2.86</v>
@@ -3140,19 +3140,19 @@
         <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
         <v>3.2</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="Q18" t="n">
         <v>2.38</v>
@@ -3293,25 +3293,25 @@
         <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.74</v>
+        <v>3.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AC18" t="n">
         <v>2.69</v>
@@ -3320,10 +3320,10 @@
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
         <v>2.12</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>3.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>2.45</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>4.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>2.97</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,65 +3746,65 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>3.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.6</v>
+        <v>1.99</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P22" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>1.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>4.16</v>
       </c>
       <c r="P23" t="n">
-        <v>3.2</v>
+        <v>4.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK23" t="n">
         <v>2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.64</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.25</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK24" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>3.62</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>4.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.09</v>
+        <v>2.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T28" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="U28" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.91</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.23</v>
+        <v>3.61</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,61 +5018,61 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>3.62</v>
+        <v>3.26</v>
       </c>
       <c r="P29" t="n">
-        <v>4.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="R29" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="S29" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T29" t="n">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W29" t="n">
         <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.61</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
         <v>1.83</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.44</v>
+        <v>6.75</v>
       </c>
       <c r="O30" t="n">
-        <v>4.73</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>6.85</v>
+        <v>1.47</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="O31" t="n">
-        <v>3.36</v>
+        <v>4.73</v>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>6.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.7</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>1.47</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P33" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK33" t="n">
         <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.76</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.82</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="P34" t="n">
-        <v>4.47</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>4.09</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S34" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T34" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.4</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,31 +5972,31 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O35" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="P35" t="n">
         <v>5.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R35" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="S35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U35" t="n">
         <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W35" t="n">
         <v>1.14</v>
@@ -6011,7 +6011,7 @@
         <v>4.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AB35" t="n">
         <v>2.35</v>
@@ -6023,7 +6023,7 @@
         <v>1.57</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
         <v>1.61</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
         <v>2.5</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="O38" t="n">
-        <v>3.93</v>
+        <v>3.68</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.25</v>
       </c>
-      <c r="T38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF38" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="O39" t="n">
-        <v>5.1</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.14</v>
       </c>
-      <c r="T39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.5</v>
+        <v>5.28</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>1.51</v>
       </c>
       <c r="O40" t="n">
-        <v>3.68</v>
+        <v>5.1</v>
       </c>
       <c r="P40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK40" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.07</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.23</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.51</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>3.78</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>4.98</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.39</v>
       </c>
-      <c r="R9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T9" t="n">
-        <v>5.15</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.67</v>
+        <v>3.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>3.07</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>5.23</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,34 +2156,34 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
         <v>3.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
@@ -2192,7 +2192,7 @@
         <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
         <v>2.17</v>
@@ -2229,7 +2229,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,16 +2318,16 @@
         <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
         <v>1.42</v>
@@ -2339,10 +2339,10 @@
         <v>2.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>2.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
         <v>1.22</v>
@@ -2372,7 +2372,7 @@
         <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
         <v>1.25</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.52</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S16" t="n">
         <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="U16" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="R17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
         <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>3.65</v>
+        <v>4.16</v>
       </c>
       <c r="P19" t="n">
-        <v>3.64</v>
+        <v>4.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="V19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.5</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.9</v>
+        <v>1.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P21" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="R21" t="n">
         <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.48</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
         <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.63</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="O23" t="n">
-        <v>4.16</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>4.32</v>
+        <v>3.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T23" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="V23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK23" t="n">
         <v>2</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="O28" t="n">
-        <v>3.62</v>
+        <v>4.73</v>
       </c>
       <c r="P28" t="n">
-        <v>4.48</v>
+        <v>6.85</v>
       </c>
       <c r="Q28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U28" t="n">
         <v>2.25</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.61</v>
+        <v>2.52</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK29" t="n">
         <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.76</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.75</v>
+        <v>2.35</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>3.15</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>4.73</v>
+        <v>3.62</v>
       </c>
       <c r="P31" t="n">
-        <v>6.85</v>
+        <v>4.48</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.8</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2.52</v>
+        <v>3.61</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P32" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.39</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.82</v>
+        <v>6.75</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>4.47</v>
+        <v>1.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>4.01</v>
+        <v>3.26</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.09</v>
+        <v>2.65</v>
       </c>
       <c r="R34" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="U34" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.91</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.23</v>
+        <v>3.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>1.51</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>5.1</v>
       </c>
       <c r="P39" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.25</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z39" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="O40" t="n">
-        <v>5.1</v>
+        <v>3.93</v>
       </c>
       <c r="P40" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R40" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.14</v>
       </c>
-      <c r="T40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.5</v>
+        <v>5.28</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>3.78</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>4.98</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.39</v>
       </c>
-      <c r="R8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T8" t="n">
-        <v>5.15</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>3.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.66</v>
+        <v>3.07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>4.98</v>
+        <v>2.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.19</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.05</v>
+        <v>5.23</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.07</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>2.19</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.23</v>
+        <v>8.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.51</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="V12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.35</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>3.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.95</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.94</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>6.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.76</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.86</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.4</v>
       </c>
-      <c r="O16" t="n">
-        <v>4</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.38</v>
-      </c>
       <c r="T16" t="n">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="U16" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3269,16 +3269,16 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R18" t="n">
         <v>2.23</v>
@@ -3290,28 +3290,28 @@
         <v>3.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V18" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AC18" t="n">
         <v>2.69</v>
@@ -3320,13 +3320,13 @@
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
         <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="P19" t="n">
-        <v>4.32</v>
+        <v>3.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="R19" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.22</v>
       </c>
-      <c r="T19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.48</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>4.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.57</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="S22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.4</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="AB22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
         <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.54</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="P27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R27" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="U27" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.44</v>
+        <v>6.75</v>
       </c>
       <c r="O28" t="n">
-        <v>4.73</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>6.85</v>
+        <v>1.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,65 +5018,65 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.82</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.87</v>
+        <v>4.01</v>
       </c>
       <c r="P29" t="n">
-        <v>4.47</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>4.09</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AG29" t="n">
         <v>2.4</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="O30" t="n">
-        <v>3.36</v>
+        <v>4.73</v>
       </c>
       <c r="P30" t="n">
-        <v>3.15</v>
+        <v>6.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.74</v>
+        <v>3.54</v>
       </c>
       <c r="O31" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="P31" t="n">
-        <v>4.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.25</v>
+        <v>4.07</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
       <c r="U31" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.04</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.61</v>
+        <v>2.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="O32" t="n">
-        <v>4.01</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.75</v>
+        <v>2.35</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="P33" t="n">
-        <v>1.47</v>
+        <v>3.15</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,61 +5813,61 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O34" t="n">
-        <v>3.26</v>
+        <v>3.62</v>
       </c>
       <c r="P34" t="n">
-        <v>3.9</v>
+        <v>4.48</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R34" t="n">
         <v>2.05</v>
       </c>
       <c r="S34" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T34" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="U34" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
         <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.9</v>
+        <v>3.61</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG34" t="n">
         <v>1.83</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,55 +5972,55 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O35" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
         <v>5.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R35" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S35" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U35" t="n">
         <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z35" t="n">
         <v>4.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
         <v>2.29</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE35" t="n">
         <v>1.18</v>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="R3" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.82</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.66</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.78</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>4.98</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.19</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>5.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.05</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.38</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>2.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.98</v>
+        <v>4.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>2.19</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>5.15</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.82</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>1.98</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q11" t="n">
         <v>2.6</v>
@@ -2174,31 +2174,31 @@
         <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
         <v>4.1</v>
@@ -2210,10 +2210,10 @@
         <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>3.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q13" t="n">
         <v>3.6</v>
@@ -2489,49 +2489,49 @@
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
         <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
         <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q18" t="n">
         <v>2.4</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>3.64</v>
+        <v>3.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
         <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="S21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1.4</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AB21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.33</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O22" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.74</v>
+        <v>3.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.05</v>
+        <v>2.45</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T22" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.88</v>
+        <v>1.63</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.63</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>6.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3.26</v>
+        <v>4.4</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>6.75</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="O29" t="n">
-        <v>4.01</v>
+        <v>3.66</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="R29" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T29" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U29" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V29" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AG29" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" t="n">
         <v>1.29</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>4.73</v>
+        <v>3.62</v>
       </c>
       <c r="P30" t="n">
-        <v>6.85</v>
+        <v>4.48</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.8</v>
       </c>
-      <c r="R30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.52</v>
+        <v>3.61</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.54</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="P31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R31" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S31" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T31" t="n">
-        <v>3.22</v>
+        <v>2.53</v>
       </c>
       <c r="U31" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>3.36</v>
       </c>
       <c r="P32" t="n">
-        <v>4.47</v>
+        <v>3.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="O33" t="n">
-        <v>3.36</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>3.15</v>
+        <v>4.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3.62</v>
+        <v>4.73</v>
       </c>
       <c r="P34" t="n">
-        <v>4.48</v>
+        <v>6.85</v>
       </c>
       <c r="Q34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U34" t="n">
         <v>2.25</v>
       </c>
-      <c r="R34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.61</v>
+        <v>2.52</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P35" t="n">
         <v>5.4</v>
@@ -6005,7 +6005,7 @@
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z35" t="n">
         <v>4.95</v>
@@ -6014,7 +6014,7 @@
         <v>1.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC35" t="n">
         <v>2.29</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="O37" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="P37" t="n">
-        <v>4.28</v>
+        <v>4.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="O39" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>4.8</v>
+        <v>4.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T39" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="U39" t="n">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="V39" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AB39" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U2" t="n">
         <v>3.4</v>
       </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y2" t="n">
         <v>1.45</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z2" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.73</v>
+        <v>4.05</v>
       </c>
       <c r="AD3" t="n">
         <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>4.65</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.68</v>
+        <v>4.21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>3.07</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>3.48</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>5.15</v>
+        <v>3.34</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>5.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>2.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.1</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.07</v>
+        <v>1.61</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.19</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.23</v>
+        <v>3.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.27</v>
+        <v>3.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>5.15</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="W10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.07</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.38</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.06</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.98</v>
+        <v>6.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R12" t="n">
         <v>2.1</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.87</v>
-      </c>
       <c r="S12" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.03</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
         <v>1.94</v>
@@ -2810,13 +2810,13 @@
         <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
         <v>2.54</v>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
         <v>1.4</v>
@@ -2978,13 +2978,13 @@
         <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
         <v>3.06</v>
@@ -2993,19 +2993,19 @@
         <v>2.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD16" t="n">
         <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
         <v>1.8</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
         <v>3.2</v>
@@ -3119,7 +3119,7 @@
         <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
         <v>2.05</v>
@@ -3128,19 +3128,19 @@
         <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.3</v>
@@ -3149,13 +3149,13 @@
         <v>3.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD17" t="n">
         <v>1.25</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,34 +3428,34 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="P19" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
         <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U19" t="n">
         <v>2.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
         <v>1.05</v>
@@ -3464,10 +3464,10 @@
         <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB19" t="n">
         <v>1.99</v>
@@ -3482,7 +3482,7 @@
         <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
         <v>2.1</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
         <v>2</v>
@@ -3590,31 +3590,31 @@
         <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="Q20" t="n">
         <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
         <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="V20" t="n">
         <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
         <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC20" t="n">
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="n">
         <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4.1</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AD21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AF21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.85</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.25</v>
       </c>
-      <c r="T22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC23" t="n">
         <v>1.63</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="R24" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
         <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK24" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,43 +4382,43 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
         <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
         <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AA25" t="n">
         <v>2.15</v>
@@ -4427,13 +4427,13 @@
         <v>1.66</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>4.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25" t="n">
         <v>2.02</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>2.01</v>
       </c>
       <c r="AK25" t="n">
         <v>1.13</v>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
         <v>4.16</v>
@@ -4556,7 +4556,7 @@
         <v>2.33</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T26" t="n">
         <v>3.15</v>
@@ -4565,7 +4565,7 @@
         <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
         <v>1.1</v>
@@ -4574,25 +4574,25 @@
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
         <v>4.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="AD26" t="n">
         <v>1.47</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
         <v>1.6</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>6.75</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.47</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.39</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.54</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.07</v>
+        <v>2.27</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T29" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U29" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.11</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AF29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.01</v>
@@ -5216,10 +5216,10 @@
         <v>3.08</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>3.61</v>
@@ -5228,7 +5228,7 @@
         <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK30" t="n">
         <v>1.89</v>
@@ -5336,55 +5336,55 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O31" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P31" t="n">
         <v>3.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S31" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V31" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
         <v>1.06</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>3.36</v>
+        <v>4.5</v>
       </c>
       <c r="P32" t="n">
-        <v>3.15</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.82</v>
+        <v>3.48</v>
       </c>
       <c r="O33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3.87</v>
-      </c>
-      <c r="P33" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.2</v>
       </c>
       <c r="R33" t="n">
         <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T33" t="n">
         <v>3.3</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.49</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AK33" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>4.73</v>
+        <v>4.01</v>
       </c>
       <c r="P34" t="n">
-        <v>6.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK34" t="n">
         <v>1.25</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6131,46 +6131,46 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P36" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S36" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T36" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="U36" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="n">
         <v>1.76</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB36" t="n">
         <v>2.7</v>
@@ -6179,16 +6179,16 @@
         <v>2.03</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AE36" t="n">
         <v>1.33</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="O37" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.8</v>
+        <v>4.37</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="R37" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="S37" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="V37" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB37" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="R38" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="S38" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="V38" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.83</v>
+        <v>7.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.67</v>
+        <v>3.41</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.54</v>
+        <v>2.46</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P39" t="n">
-        <v>4.28</v>
+        <v>2.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.25</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AF39" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6773,19 +6773,19 @@
         <v>3.93</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S40" t="n">
         <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="U40" t="n">
         <v>2.23</v>
@@ -6794,7 +6794,7 @@
         <v>1.63</v>
       </c>
       <c r="W40" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -6803,28 +6803,28 @@
         <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="AA40" t="n">
         <v>1.53</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
         <v>2.76</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>3.96</v>
       </c>
       <c r="O19" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="P19" t="n">
-        <v>3.95</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S19" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="T19" t="n">
-        <v>2.91</v>
+        <v>4.05</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.99</v>
+        <v>2.95</v>
       </c>
       <c r="AC19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
         <v>2.88</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.88</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.96</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
         <v>4.12</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="R24" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="T24" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="O27" t="n">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>4.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T27" t="n">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.53</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.55</v>
+        <v>3.61</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.56</v>
+        <v>1.89</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.36</v>
+        <v>4.01</v>
       </c>
       <c r="P28" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.62</v>
       </c>
-      <c r="P30" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="AA30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.8</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AD30" t="n">
         <v>1.36</v>
       </c>
-      <c r="W30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="P31" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.66</v>
+        <v>1.94</v>
       </c>
       <c r="R31" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="S31" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U31" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.03</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.76</v>
+        <v>4.53</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.19</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC31" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>3.48</v>
       </c>
       <c r="O32" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P32" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.48</v>
+        <v>2.01</v>
       </c>
       <c r="O33" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.03</v>
+        <v>3.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.87</v>
+        <v>2.66</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.3</v>
       </c>
-      <c r="T33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.51</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.15</v>
+        <v>2.76</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
-        <v>4.01</v>
+        <v>3.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>4.37</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="S37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>3.93</v>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="S38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.17</v>
       </c>
-      <c r="T38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Z38" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.41</v>
+        <v>2.29</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.35</v>
       </c>
-      <c r="O39" t="n">
+      <c r="S39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.6</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U39" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V39" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
-        <v>3.93</v>
+        <v>4.5</v>
       </c>
       <c r="P40" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="R40" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="S40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.25</v>
       </c>
-      <c r="T40" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.29</v>
+        <v>3.41</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.82</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="AG2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.3</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.65</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.21</v>
+        <v>3.15</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.07</v>
+        <v>1.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.48</v>
+        <v>2.19</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.23</v>
+        <v>3.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.36</v>
+        <v>3.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.61</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.98</v>
+        <v>1.37</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.1</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.87</v>
-      </c>
       <c r="S13" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>4.77</v>
       </c>
       <c r="R15" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.38</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.77</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
         <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.3</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.06</v>
+        <v>3.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,28 +3110,28 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P17" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S17" t="n">
         <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
@@ -3143,31 +3143,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.7</v>
+        <v>2.54</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="U20" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>1.21</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="T24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.65</v>
       </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,61 +4700,61 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="O27" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>4.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="R27" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S27" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
         <v>1.83</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>1.74</v>
       </c>
       <c r="O28" t="n">
-        <v>4.01</v>
+        <v>3.62</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>4.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.41</v>
+        <v>2.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="S28" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="T28" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="U28" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="V28" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z28" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7</v>
+        <v>1.73</v>
       </c>
       <c r="O29" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>4.01</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.27</v>
+        <v>3.41</v>
       </c>
       <c r="R30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.18</v>
       </c>
-      <c r="S30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z30" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.2</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.01</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P33" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="O34" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="P34" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R37" t="n">
         <v>2.35</v>
       </c>
-      <c r="O37" t="n">
+      <c r="S37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.6</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U37" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V37" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W37" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="O38" t="n">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.44</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="S38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T38" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U38" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V38" t="n">
         <v>1.63</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,40 +6608,40 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="O39" t="n">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="P39" t="n">
-        <v>4.37</v>
+        <v>3.44</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="S39" t="n">
         <v>1.25</v>
       </c>
       <c r="T39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U39" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="V39" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W39" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
         <v>5.25</v>
@@ -6650,22 +6650,22 @@
         <v>1.53</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE39" t="n">
         <v>1.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.21</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.82</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.61</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.98</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.07</v>
+        <v>1.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.48</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="S9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.26</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.23</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.31</v>
+        <v>3.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>2.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.65</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.37</v>
+        <v>6.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.09</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="R10" t="n">
-        <v>3.45</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>5.15</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>6.65</v>
+        <v>1.96</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,16 +2159,16 @@
         <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
         <v>3.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>1.46</v>
@@ -2177,19 +2177,19 @@
         <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.05</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
         <v>3.03</v>
@@ -2204,7 +2204,7 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
         <v>1.04</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.87</v>
@@ -2336,19 +2336,19 @@
         <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
         <v>2.59</v>
@@ -2363,7 +2363,7 @@
         <v>4.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2372,7 +2372,7 @@
         <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.03</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.88</v>
       </c>
-      <c r="U13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
         <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="P14" t="n">
-        <v>8.5</v>
+        <v>14.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T14" t="n">
-        <v>3.21</v>
+        <v>3.32</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.45</v>
+        <v>4.68</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P15" t="n">
         <v>3.25</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q15" t="n">
-        <v>4.77</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
         <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
         <v>3.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
         <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>1.42</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2</v>
+        <v>6.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.38</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.7</v>
+        <v>2.79</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>4.77</v>
       </c>
       <c r="R17" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.38</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.78</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="Q18" t="n">
         <v>2.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S18" t="n">
         <v>1.32</v>
@@ -3302,31 +3302,31 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
         <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AC18" t="n">
         <v>2.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="n">
         <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="V20" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="O21" t="n">
-        <v>3.82</v>
+        <v>4.12</v>
       </c>
       <c r="P21" t="n">
-        <v>3.95</v>
+        <v>3.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>1.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
-        <v>4.12</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.63</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="P23" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="R23" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="U23" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="R25" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V25" t="n">
         <v>1.3</v>
@@ -4418,25 +4418,25 @@
         <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
         <v>1.01</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
         <v>1.67</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AK25" t="n">
         <v>1.13</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.01</v>
+        <v>3.48</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.66</v>
+        <v>3.87</v>
       </c>
       <c r="R27" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="V27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.62</v>
+        <v>3.36</v>
       </c>
       <c r="P28" t="n">
-        <v>4.48</v>
+        <v>3.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.05</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AD29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="P31" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.48</v>
+        <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="O33" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.47</v>
+        <v>6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="R34" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="U34" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V34" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.2</v>
       </c>
       <c r="AF34" t="n">
         <v>1.7</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,34 +5972,34 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="O35" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
         <v>5.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S35" t="n">
         <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U35" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V35" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
@@ -6020,16 +6020,16 @@
         <v>2.29</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>4.37</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="S37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R38" t="n">
         <v>2.35</v>
       </c>
-      <c r="O38" t="n">
+      <c r="S38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.6</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V38" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
-        <v>3.93</v>
+        <v>4.5</v>
       </c>
       <c r="P39" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="R39" t="n">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="S39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.25</v>
       </c>
-      <c r="T39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.12</v>
-      </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.29</v>
+        <v>3.41</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.38</v>
+        <v>1.81</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.59</v>
+        <v>2.03</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="O40" t="n">
-        <v>4.5</v>
+        <v>3.93</v>
       </c>
       <c r="P40" t="n">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="S40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>1.17</v>
       </c>
-      <c r="T40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Z40" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.41</v>
+        <v>2.29</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -638,61 +638,61 @@
         <v>4.3</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="O3">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="O4">
+        <v>2.9</v>
+      </c>
+      <c r="P4">
+        <v>2.45</v>
+      </c>
+      <c r="Q4">
         <v>3.15</v>
       </c>
-      <c r="P4">
-        <v>3.65</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
       <c r="R4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="V8">
         <v>1.38</v>
@@ -1643,34 +1643,34 @@
         <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.2</v>
+        <v>3.07</v>
       </c>
       <c r="O9">
-        <v>8.24</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>11.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q9">
-        <v>1.49</v>
+        <v>3.48</v>
       </c>
       <c r="R9">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="V9">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA9">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
-        <v>3.24</v>
+        <v>2.29</v>
       </c>
       <c r="AC9">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="AD9">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AE9">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>4.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="P10">
-        <v>2.05</v>
+        <v>15</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="Q11">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="AA11">
         <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC11">
         <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
         <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="Q12">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="AA12">
         <v>2.05</v>
       </c>
       <c r="AB12">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
         <v>1.25</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P13">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="P14">
-        <v>9.5</v>
+        <v>14.8</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
+        <v>2.01</v>
+      </c>
+      <c r="Q15">
+        <v>4.59</v>
+      </c>
+      <c r="R15">
         <v>2</v>
       </c>
-      <c r="Q15">
-        <v>4.33</v>
-      </c>
-      <c r="R15">
-        <v>1.94</v>
-      </c>
       <c r="S15">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>1.38</v>
+      </c>
+      <c r="Z15">
+        <v>3.08</v>
+      </c>
+      <c r="AA15">
+        <v>2.2</v>
+      </c>
+      <c r="AB15">
+        <v>1.65</v>
+      </c>
+      <c r="AC15">
+        <v>3.9</v>
+      </c>
+      <c r="AD15">
+        <v>1.22</v>
+      </c>
+      <c r="AE15">
         <v>1.03</v>
       </c>
-      <c r="Y15">
-        <v>1.41</v>
-      </c>
-      <c r="Z15">
-        <v>2.91</v>
-      </c>
-      <c r="AA15">
-        <v>2.05</v>
-      </c>
-      <c r="AB15">
-        <v>1.68</v>
-      </c>
-      <c r="AC15">
-        <v>4.1</v>
-      </c>
-      <c r="AD15">
-        <v>1.2</v>
-      </c>
-      <c r="AE15">
-        <v>1.02</v>
-      </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>6.75</v>
       </c>
       <c r="Q16">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="S16">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB16">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC16">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.64</v>
+        <v>2.79</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC17">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="AD17">
+        <v>1.25</v>
+      </c>
+      <c r="AE17">
+        <v>1.05</v>
+      </c>
+      <c r="AF17">
+        <v>1.8</v>
+      </c>
+      <c r="AG17">
+        <v>1.96</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.3</v>
       </c>
-      <c r="AE17">
-        <v>1.1</v>
-      </c>
-      <c r="AF17">
-        <v>2.1</v>
-      </c>
-      <c r="AG17">
-        <v>1.62</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.18</v>
-      </c>
       <c r="AK17">
-        <v>2.79</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>4.51</v>
+        <v>3.34</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB19">
+        <v>1.99</v>
+      </c>
+      <c r="AC19">
+        <v>2.88</v>
+      </c>
+      <c r="AD19">
+        <v>1.4</v>
+      </c>
+      <c r="AE19">
+        <v>1.13</v>
+      </c>
+      <c r="AF19">
+        <v>1.65</v>
+      </c>
+      <c r="AG19">
+        <v>2.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.26</v>
+      </c>
+      <c r="AK19">
         <v>2</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.59</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
-        <v>4.89</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>5.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC20">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AD20">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="O21">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>4.68</v>
+        <v>3.72</v>
       </c>
       <c r="Q21">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
+        <v>1.29</v>
+      </c>
+      <c r="T21">
+        <v>3.3</v>
+      </c>
+      <c r="U21">
+        <v>2.4</v>
+      </c>
+      <c r="V21">
+        <v>1.5</v>
+      </c>
+      <c r="W21">
+        <v>1.12</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
         <v>1.22</v>
       </c>
-      <c r="T21">
-        <v>3.85</v>
-      </c>
-      <c r="U21">
-        <v>2.07</v>
-      </c>
-      <c r="V21">
-        <v>1.65</v>
-      </c>
-      <c r="W21">
-        <v>1.14</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>1.14</v>
-      </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD21">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.56</v>
+        <v>1.99</v>
       </c>
       <c r="O22">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AA22">
         <v>1.36</v>
@@ -3940,19 +3940,19 @@
         <v>3.1</v>
       </c>
       <c r="AC22">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AD22">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE22">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="O23">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
+        <v>1.22</v>
+      </c>
+      <c r="T23">
+        <v>3.9</v>
+      </c>
+      <c r="U23">
+        <v>2.17</v>
+      </c>
+      <c r="V23">
+        <v>1.67</v>
+      </c>
+      <c r="W23">
+        <v>1.15</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>1.09</v>
+      </c>
+      <c r="Z23">
+        <v>5.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.48</v>
+      </c>
+      <c r="AB23">
+        <v>2.6</v>
+      </c>
+      <c r="AC23">
+        <v>2.2</v>
+      </c>
+      <c r="AD23">
+        <v>1.65</v>
+      </c>
+      <c r="AE23">
         <v>1.25</v>
       </c>
-      <c r="T23">
-        <v>3.4</v>
-      </c>
-      <c r="U23">
-        <v>2.34</v>
-      </c>
-      <c r="V23">
-        <v>1.55</v>
-      </c>
-      <c r="W23">
-        <v>1.11</v>
-      </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
-      <c r="Y23">
-        <v>1.2</v>
-      </c>
-      <c r="Z23">
-        <v>4.2</v>
-      </c>
-      <c r="AA23">
-        <v>1.62</v>
-      </c>
-      <c r="AB23">
-        <v>2.15</v>
-      </c>
-      <c r="AC23">
-        <v>2.65</v>
-      </c>
-      <c r="AD23">
+      <c r="AF23">
         <v>1.45</v>
       </c>
-      <c r="AE23">
-        <v>1.17</v>
-      </c>
-      <c r="AF23">
-        <v>1.58</v>
-      </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
         <v>1.7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,58 +4547,58 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>4.08</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>4.94</v>
+        <v>4.12</v>
       </c>
       <c r="Q26">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
         <v>3.4</v>
       </c>
       <c r="U26">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z26">
         <v>4.36</v>
       </c>
       <c r="AA26">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AD26">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
         <v>1.6</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="P28">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O29">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.32</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
+        <v>2.63</v>
+      </c>
+      <c r="R29">
+        <v>1.96</v>
+      </c>
+      <c r="S29">
+        <v>1.47</v>
+      </c>
+      <c r="T29">
         <v>2.5</v>
-      </c>
-      <c r="R29">
-        <v>1.99</v>
-      </c>
-      <c r="S29">
-        <v>1.46</v>
-      </c>
-      <c r="T29">
-        <v>2.53</v>
       </c>
       <c r="U29">
         <v>3.1</v>
@@ -5066,28 +5066,28 @@
         <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA29">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB29">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC29">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD29">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.91</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="P30">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>4.07</v>
+        <v>3.75</v>
       </c>
       <c r="R30">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="S30">
         <v>1.3</v>
@@ -5220,43 +5220,43 @@
         <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="O31">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="R31">
         <v>2.45</v>
       </c>
       <c r="S31">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
         <v>1.15</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA31">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB31">
         <v>2.3</v>
       </c>
       <c r="AC31">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AD31">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE31">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="O32">
-        <v>4.79</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>7.12</v>
+        <v>3.57</v>
       </c>
       <c r="Q32">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="R32">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="U32">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
       <c r="V32">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
+        <v>1.24</v>
+      </c>
+      <c r="Z32">
+        <v>4</v>
+      </c>
+      <c r="AA32">
+        <v>1.75</v>
+      </c>
+      <c r="AB32">
+        <v>2</v>
+      </c>
+      <c r="AC32">
+        <v>2.8</v>
+      </c>
+      <c r="AD32">
+        <v>1.41</v>
+      </c>
+      <c r="AE32">
+        <v>1.11</v>
+      </c>
+      <c r="AF32">
+        <v>1.7</v>
+      </c>
+      <c r="AG32">
+        <v>2.04</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.2</v>
       </c>
-      <c r="Z32">
-        <v>5</v>
-      </c>
-      <c r="AA32">
-        <v>1.55</v>
-      </c>
-      <c r="AB32">
-        <v>2.45</v>
-      </c>
-      <c r="AC32">
-        <v>2.25</v>
-      </c>
-      <c r="AD32">
-        <v>1.55</v>
-      </c>
-      <c r="AE32">
-        <v>1.18</v>
-      </c>
-      <c r="AF32">
-        <v>1.73</v>
-      </c>
-      <c r="AG32">
-        <v>2.1</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.18</v>
-      </c>
       <c r="AK32">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="O33">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="P33">
-        <v>4.79</v>
+        <v>1.99</v>
       </c>
       <c r="Q33">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="R33">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="V33">
+        <v>1.61</v>
+      </c>
+      <c r="W33">
+        <v>1.17</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>1.16</v>
+      </c>
+      <c r="Z33">
+        <v>5.17</v>
+      </c>
+      <c r="AA33">
+        <v>1.54</v>
+      </c>
+      <c r="AB33">
+        <v>2.49</v>
+      </c>
+      <c r="AC33">
+        <v>2.23</v>
+      </c>
+      <c r="AD33">
+        <v>1.63</v>
+      </c>
+      <c r="AE33">
+        <v>1.24</v>
+      </c>
+      <c r="AF33">
         <v>1.5</v>
       </c>
-      <c r="W33">
-        <v>1.11</v>
-      </c>
-      <c r="X33">
-        <v>1.04</v>
-      </c>
-      <c r="Y33">
-        <v>1.24</v>
-      </c>
-      <c r="Z33">
-        <v>3.7</v>
-      </c>
-      <c r="AA33">
-        <v>1.65</v>
-      </c>
-      <c r="AB33">
-        <v>2.1</v>
-      </c>
-      <c r="AC33">
-        <v>2.88</v>
-      </c>
-      <c r="AD33">
-        <v>1.41</v>
-      </c>
-      <c r="AE33">
-        <v>1.15</v>
-      </c>
-      <c r="AF33">
-        <v>1.67</v>
-      </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O35">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P35">
-        <v>5.54</v>
+        <v>5.4</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R35">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
         <v>3.58</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V35">
         <v>1.59</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
         <v>4.95</v>
       </c>
       <c r="AA35">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="AD35">
         <v>1.43</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG35">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="O36">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="P36">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q36">
+        <v>2.5</v>
+      </c>
+      <c r="R36">
         <v>2.45</v>
       </c>
-      <c r="R36">
-        <v>2.66</v>
-      </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U36">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V36">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB36">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AC36">
         <v>2.1</v>
       </c>
       <c r="AD36">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE36">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF36">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG36">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O37">
         <v>3.93</v>
       </c>
       <c r="P37">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q37">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R37">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U37">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
         <v>1.6</v>
@@ -6373,31 +6373,31 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>5.1</v>
+        <v>5.02</v>
       </c>
       <c r="AA37">
+        <v>1.57</v>
+      </c>
+      <c r="AB37">
+        <v>2.4</v>
+      </c>
+      <c r="AC37">
+        <v>2.35</v>
+      </c>
+      <c r="AD37">
         <v>1.55</v>
       </c>
-      <c r="AB37">
-        <v>2.52</v>
-      </c>
-      <c r="AC37">
-        <v>2.25</v>
-      </c>
-      <c r="AD37">
-        <v>1.57</v>
-      </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
         <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O38">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="P38">
-        <v>6.18</v>
+        <v>5.1</v>
       </c>
       <c r="Q38">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R38">
         <v>2.95</v>
       </c>
       <c r="S38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T38">
         <v>4.8</v>
       </c>
       <c r="U38">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V38">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="W38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X38">
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA38">
         <v>1.29</v>
       </c>
       <c r="AB38">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="AC38">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AD38">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AE38">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.11</v>
       </c>
       <c r="AK38">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="P39">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="V39">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB39">
         <v>2.6</v>
       </c>
       <c r="AC39">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD39">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
         <v>1.53</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O40">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>4.47</v>
+        <v>4.37</v>
       </c>
       <c r="Q40">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
+        <v>1.12</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
         <v>1.13</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>1.17</v>
-      </c>
       <c r="Z40">
-        <v>5.06</v>
+        <v>5.25</v>
       </c>
       <c r="AA40">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AC40">
         <v>2.25</v>
       </c>
       <c r="AD40">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE40">
         <v>1.23</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
         <v>2.05</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>1.82</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>4.21</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T2">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>1.4</v>
+      </c>
+      <c r="Z2">
+        <v>2.92</v>
+      </c>
+      <c r="AA2">
+        <v>2.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.65</v>
+      </c>
+      <c r="AC2">
+        <v>4.05</v>
+      </c>
+      <c r="AD2">
+        <v>1.23</v>
+      </c>
+      <c r="AE2">
         <v>1.06</v>
       </c>
-      <c r="Y2">
-        <v>1.31</v>
-      </c>
-      <c r="Z2">
-        <v>2.94</v>
-      </c>
-      <c r="AA2">
-        <v>2.05</v>
-      </c>
-      <c r="AB2">
-        <v>1.75</v>
-      </c>
-      <c r="AC2">
-        <v>3.44</v>
-      </c>
-      <c r="AD2">
+      <c r="AF2">
+        <v>1.85</v>
+      </c>
+      <c r="AG2">
+        <v>1.72</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.28</v>
       </c>
-      <c r="AE2">
-        <v>1.07</v>
-      </c>
-      <c r="AF2">
-        <v>1.89</v>
-      </c>
-      <c r="AG2">
-        <v>1.81</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.3</v>
-      </c>
       <c r="AK2">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.82</v>
+        <v>4.3</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>4.21</v>
       </c>
       <c r="R3">
+        <v>2.07</v>
+      </c>
+      <c r="S3">
+        <v>1.44</v>
+      </c>
+      <c r="T3">
+        <v>2.54</v>
+      </c>
+      <c r="U3">
+        <v>2.82</v>
+      </c>
+      <c r="V3">
+        <v>1.35</v>
+      </c>
+      <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.06</v>
+      </c>
+      <c r="Y3">
+        <v>1.31</v>
+      </c>
+      <c r="Z3">
+        <v>2.94</v>
+      </c>
+      <c r="AA3">
         <v>2.05</v>
       </c>
-      <c r="S3">
-        <v>1.47</v>
-      </c>
-      <c r="T3">
-        <v>2.66</v>
-      </c>
-      <c r="U3">
-        <v>3.22</v>
-      </c>
-      <c r="V3">
-        <v>1.33</v>
-      </c>
-      <c r="W3">
-        <v>1.01</v>
-      </c>
-      <c r="X3">
-        <v>1.05</v>
-      </c>
-      <c r="Y3">
-        <v>1.4</v>
-      </c>
-      <c r="Z3">
-        <v>2.92</v>
-      </c>
-      <c r="AA3">
-        <v>2.25</v>
-      </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG3">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.97</v>
+        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>3.3</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R13">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
         <v>1.51</v>
@@ -2461,10 +2461,10 @@
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z13">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AA13">
         <v>2.45</v>
@@ -2597,7 +2597,7 @@
         <v>7.1</v>
       </c>
       <c r="P14">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>1.6</v>
@@ -2606,19 +2606,19 @@
         <v>2.8</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
         <v>1.56</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2633,13 +2633,13 @@
         <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC14">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD14">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE14">
         <v>1.18</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q25">
         <v>5.61</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T25">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="U25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4417,28 +4417,28 @@
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z25">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="AD25">
         <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG25">
         <v>1.67</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>1.13</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -2431,40 +2431,40 @@
         <v>2.05</v>
       </c>
       <c r="O13">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q13">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R13">
         <v>1.95</v>
       </c>
       <c r="S13">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T13">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U13">
         <v>3.25</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W13">
         <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AA13">
         <v>2.45</v>
@@ -2479,10 +2479,10 @@
         <v>1.13</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
         <v>1.67</v>
@@ -2501,7 +2501,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O14">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="P14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="S14">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="U14">
         <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.35</v>
+        <v>4.59</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD14">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG14">
         <v>1.57</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK14">
-        <v>4.68</v>
+        <v>4.35</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U25">
         <v>3.25</v>
@@ -4417,16 +4417,16 @@
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA25">
         <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC25">
         <v>4.27</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
         <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="U2">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="AA2">
         <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
         <v>4.05</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
         <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.3</v>
+        <v>3.87</v>
       </c>
       <c r="O3">
         <v>3.4</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q3">
         <v>4.21</v>
       </c>
       <c r="R3">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
         <v>1.04</v>
-      </c>
-      <c r="X3">
-        <v>1.06</v>
       </c>
       <c r="Y3">
         <v>1.31</v>
@@ -837,25 +837,25 @@
         <v>2.94</v>
       </c>
       <c r="AA3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG3">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>2.63</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="P4">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q4">
         <v>3.15</v>
@@ -991,34 +991,34 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z4">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AA4">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC4">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD4">
         <v>1.15</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>4.51</v>
       </c>
       <c r="Q8">
         <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S8">
         <v>1.36</v>
@@ -1634,59 +1634,59 @@
         <v>2.88</v>
       </c>
       <c r="U8">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.31</v>
+      </c>
+      <c r="Z8">
+        <v>3.09</v>
+      </c>
+      <c r="AA8">
+        <v>2.05</v>
+      </c>
+      <c r="AB8">
+        <v>1.75</v>
+      </c>
+      <c r="AC8">
+        <v>3.55</v>
+      </c>
+      <c r="AD8">
+        <v>1.24</v>
+      </c>
+      <c r="AE8">
+        <v>1.05</v>
+      </c>
+      <c r="AF8">
+        <v>1.95</v>
+      </c>
+      <c r="AG8">
+        <v>1.77</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.29</v>
       </c>
-      <c r="Z8">
-        <v>3.05</v>
-      </c>
-      <c r="AA8">
-        <v>2</v>
-      </c>
-      <c r="AB8">
-        <v>1.8</v>
-      </c>
-      <c r="AC8">
-        <v>3.6</v>
-      </c>
-      <c r="AD8">
-        <v>1.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.06</v>
-      </c>
-      <c r="AF8">
-        <v>1.92</v>
-      </c>
-      <c r="AG8">
-        <v>1.76</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.25</v>
-      </c>
       <c r="AK8">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>3.07</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q9">
         <v>3.48</v>
@@ -1791,13 +1791,13 @@
         <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.6</v>
@@ -1815,16 +1815,16 @@
         <v>4.6</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AC9">
         <v>2.36</v>
       </c>
       <c r="AD9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE9">
         <v>1.19</v>
@@ -1833,7 +1833,7 @@
         <v>1.45</v>
       </c>
       <c r="AG9">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O10">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="P10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q10">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="R10">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T10">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="U10">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V10">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="W10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AC10">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD10">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE10">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG10">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.01</v>
       </c>
       <c r="AK10">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
         <v>1.46</v>
       </c>
       <c r="T11">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U11">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
+        <v>1.34</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
         <v>1.35</v>
       </c>
-      <c r="W11">
-        <v>1.04</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.36</v>
-      </c>
       <c r="Z11">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AA11">
         <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
         <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P12">
         <v>2.05</v>
       </c>
       <c r="Q12">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.28</v>
@@ -2313,13 +2313,13 @@
         <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
         <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
         <v>1.87</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>1.53</v>
       </c>
       <c r="R14">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="S14">
         <v>1.25</v>
@@ -2615,7 +2615,7 @@
         <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2630,25 +2630,25 @@
         <v>4.59</v>
       </c>
       <c r="AA14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
         <v>2.35</v>
       </c>
       <c r="AC14">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AD14">
         <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
         <v>2.25</v>
       </c>
       <c r="AG14">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.02</v>
       </c>
       <c r="AK14">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,43 +2754,43 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.02</v>
+        <v>4.15</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>4.59</v>
+        <v>4.77</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
         <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
@@ -2799,13 +2799,13 @@
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>1.91</v>
@@ -2827,7 +2827,7 @@
         <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="P16">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R16">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U16">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="V16">
         <v>1.38</v>
@@ -2947,25 +2947,25 @@
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA16">
         <v>1.99</v>
       </c>
       <c r="AB16">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC16">
         <v>3.4</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -2990,7 +2990,7 @@
         <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>2.1</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
         <v>3.25</v>
@@ -3098,46 +3098,46 @@
         <v>1.43</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
         <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>3.68</v>
+        <v>3.91</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R18">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
         <v>3.25</v>
@@ -3273,34 +3273,34 @@
         <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AA18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AD18">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.34</v>
+        <v>3.43</v>
       </c>
       <c r="Q19">
         <v>2.25</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P20">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q20">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.19</v>
@@ -3590,19 +3590,19 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
         <v>6.41</v>
@@ -3611,19 +3611,19 @@
         <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AC20">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD20">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
         <v>2.88</v>
@@ -3732,40 +3732,40 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O21">
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.72</v>
+        <v>3.46</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
         <v>3.3</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
         <v>4</v>
@@ -3774,22 +3774,22 @@
         <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AC21">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="O22">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
         <v>2.9</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB22">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC22">
         <v>1.63</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="Q23">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R23">
         <v>2.45</v>
@@ -4076,43 +4076,43 @@
         <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U23">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="V23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
         <v>1.15</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>5.4</v>
+        <v>5.62</v>
       </c>
       <c r="AA23">
         <v>1.48</v>
       </c>
       <c r="AB23">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AC23">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD23">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE23">
         <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
         <v>2.55</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4227,10 +4227,10 @@
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="Q24">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R24">
         <v>2</v>
@@ -4239,7 +4239,7 @@
         <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="U24">
         <v>2.88</v>
@@ -4248,37 +4248,37 @@
         <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z24">
         <v>2.88</v>
       </c>
       <c r="AA24">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB24">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
         <v>4.1</v>
       </c>
       <c r="AD24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
         <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T25">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
         <v>3.25</v>
@@ -4411,7 +4411,7 @@
         <v>1.27</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4420,28 +4420,28 @@
         <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB25">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AD25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,52 +4547,52 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
         <v>4.12</v>
       </c>
       <c r="Q26">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S26">
         <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.17</v>
       </c>
       <c r="Z26">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="AA26">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB26">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC26">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
         <v>1.47</v>
@@ -4604,7 +4604,7 @@
         <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="O28">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
         <v>1.47</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="P29">
         <v>3.9</v>
       </c>
       <c r="Q29">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.47</v>
@@ -5060,13 +5060,13 @@
         <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.34</v>
@@ -5078,7 +5078,7 @@
         <v>2.23</v>
       </c>
       <c r="AB29">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
@@ -5087,7 +5087,7 @@
         <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.91</v>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,46 +5199,46 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="O30">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q30">
         <v>3.75</v>
       </c>
       <c r="R30">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
         <v>2.2</v>
@@ -5250,13 +5250,13 @@
         <v>1.48</v>
       </c>
       <c r="AE30">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O31">
         <v>4.2</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R31">
         <v>2.45</v>
@@ -5380,62 +5380,62 @@
         <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="U31">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="V31">
+        <v>1.56</v>
+      </c>
+      <c r="W31">
+        <v>1.11</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.21</v>
+      </c>
+      <c r="Z31">
+        <v>4.75</v>
+      </c>
+      <c r="AA31">
         <v>1.57</v>
       </c>
-      <c r="W31">
+      <c r="AB31">
+        <v>2.17</v>
+      </c>
+      <c r="AC31">
+        <v>2.55</v>
+      </c>
+      <c r="AD31">
+        <v>1.5</v>
+      </c>
+      <c r="AE31">
+        <v>1.2</v>
+      </c>
+      <c r="AF31">
+        <v>1.7</v>
+      </c>
+      <c r="AG31">
+        <v>2.05</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.15</v>
       </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.2</v>
-      </c>
-      <c r="Z31">
-        <v>4.4</v>
-      </c>
-      <c r="AA31">
-        <v>1.55</v>
-      </c>
-      <c r="AB31">
-        <v>2.3</v>
-      </c>
-      <c r="AC31">
-        <v>2.36</v>
-      </c>
-      <c r="AD31">
-        <v>1.55</v>
-      </c>
-      <c r="AE31">
-        <v>1.21</v>
-      </c>
-      <c r="AF31">
-        <v>1.67</v>
-      </c>
-      <c r="AG31">
-        <v>2</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.14</v>
-      </c>
       <c r="AK31">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="P32">
-        <v>3.57</v>
+        <v>4.32</v>
       </c>
       <c r="Q32">
         <v>2.27</v>
@@ -5540,13 +5540,13 @@
         <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="U32">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="V32">
         <v>1.46</v>
@@ -5558,31 +5558,31 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC32">
         <v>2.8</v>
       </c>
       <c r="AD32">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>1.99</v>
       </c>
       <c r="Q33">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
         <v>2.38</v>
@@ -5706,7 +5706,7 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U33">
         <v>2.13</v>
@@ -5715,10 +5715,10 @@
         <v>1.61</v>
       </c>
       <c r="W33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.16</v>
@@ -5739,13 +5739,13 @@
         <v>1.63</v>
       </c>
       <c r="AE33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
         <v>1.3</v>
@@ -5860,55 +5860,55 @@
         <v>4.48</v>
       </c>
       <c r="Q34">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U34">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z34">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA34">
         <v>2.02</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC34">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,13 +6023,13 @@
         <v>5.4</v>
       </c>
       <c r="Q35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T35">
         <v>3.58</v>
@@ -6038,10 +6038,10 @@
         <v>2.23</v>
       </c>
       <c r="V35">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6056,22 +6056,22 @@
         <v>1.47</v>
       </c>
       <c r="AB35">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AC35">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD35">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>2.04</v>
       </c>
       <c r="O36">
-        <v>4.01</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
         <v>2.8</v>
@@ -6189,16 +6189,16 @@
         <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
         <v>3.94</v>
       </c>
       <c r="U36">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V36">
         <v>1.67</v>
@@ -6210,31 +6210,31 @@
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA36">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD36">
         <v>1.73</v>
       </c>
       <c r="AE36">
+        <v>1.34</v>
+      </c>
+      <c r="AF36">
         <v>1.33</v>
       </c>
-      <c r="AF36">
-        <v>1.36</v>
-      </c>
       <c r="AG36">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O37">
-        <v>3.93</v>
+        <v>3.65</v>
       </c>
       <c r="P37">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q37">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R37">
         <v>2.37</v>
       </c>
       <c r="S37">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W37">
         <v>1.13</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>5.02</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
         <v>1.55</v>
       </c>
       <c r="AE37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
         <v>1.8</v>
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O38">
-        <v>4.7</v>
+        <v>4.88</v>
       </c>
       <c r="P38">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="R38">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
         <v>1.17</v>
       </c>
       <c r="T38">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U38">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V38">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="W38">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X38">
         <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z38">
         <v>7.5</v>
       </c>
       <c r="AA38">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB38">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AC38">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD38">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AE38">
         <v>1.42</v>
@@ -6560,7 +6560,7 @@
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.11</v>
       </c>
       <c r="AK38">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O39">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
         <v>2.5</v>
@@ -6681,49 +6681,49 @@
         <v>2.38</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB39">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC39">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD39">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
         <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O40">
         <v>3.8</v>
       </c>
       <c r="P40">
-        <v>4.37</v>
+        <v>4</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R40">
         <v>2.35</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U40">
         <v>2.25</v>
@@ -6859,16 +6859,16 @@
         <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA40">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB40">
         <v>2.3</v>
@@ -6877,16 +6877,16 @@
         <v>2.25</v>
       </c>
       <c r="AD40">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE40">
         <v>1.23</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
         <v>2.05</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>3.51</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>4.32</v>
       </c>
       <c r="Q31">
-        <v>1.93</v>
+        <v>2.27</v>
       </c>
       <c r="R31">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="U31">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="V31">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.75</v>
+        <v>3.97</v>
       </c>
       <c r="AA31">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD31">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
         <v>2.05</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="O32">
-        <v>3.51</v>
+        <v>4.01</v>
       </c>
       <c r="P32">
-        <v>4.32</v>
+        <v>1.99</v>
       </c>
       <c r="Q32">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="R32">
         <v>2.38</v>
       </c>
       <c r="S32">
+        <v>1.25</v>
+      </c>
+      <c r="T32">
+        <v>3.7</v>
+      </c>
+      <c r="U32">
+        <v>2.13</v>
+      </c>
+      <c r="V32">
+        <v>1.61</v>
+      </c>
+      <c r="W32">
+        <v>1.15</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.16</v>
+      </c>
+      <c r="Z32">
+        <v>5.17</v>
+      </c>
+      <c r="AA32">
+        <v>1.54</v>
+      </c>
+      <c r="AB32">
+        <v>2.49</v>
+      </c>
+      <c r="AC32">
+        <v>2.23</v>
+      </c>
+      <c r="AD32">
+        <v>1.63</v>
+      </c>
+      <c r="AE32">
+        <v>1.2</v>
+      </c>
+      <c r="AF32">
+        <v>1.5</v>
+      </c>
+      <c r="AG32">
+        <v>2.55</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.19</v>
+      </c>
+      <c r="AK32">
         <v>1.3</v>
-      </c>
-      <c r="T32">
-        <v>2.86</v>
-      </c>
-      <c r="U32">
-        <v>2.64</v>
-      </c>
-      <c r="V32">
-        <v>1.46</v>
-      </c>
-      <c r="W32">
-        <v>1.08</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
-      <c r="Z32">
-        <v>3.97</v>
-      </c>
-      <c r="AA32">
-        <v>1.75</v>
-      </c>
-      <c r="AB32">
-        <v>1.96</v>
-      </c>
-      <c r="AC32">
-        <v>2.8</v>
-      </c>
-      <c r="AD32">
-        <v>1.4</v>
-      </c>
-      <c r="AE32">
-        <v>1.14</v>
-      </c>
-      <c r="AF32">
-        <v>1.67</v>
-      </c>
-      <c r="AG32">
-        <v>2.05</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.2</v>
-      </c>
-      <c r="AK32">
-        <v>2.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="O33">
-        <v>4.01</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="U33">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="V33">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>5.17</v>
+        <v>4.75</v>
       </c>
       <c r="AA33">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="AC33">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AD33">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
         <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>2.63</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="O37">
-        <v>3.65</v>
+        <v>4.88</v>
       </c>
       <c r="P37">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q37">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="R37">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="V37">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z37">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA37">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC37">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AD37">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AF37">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="O38">
-        <v>4.88</v>
+        <v>3.78</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="V38">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="W38">
+        <v>1.15</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.13</v>
+      </c>
+      <c r="Z38">
+        <v>6</v>
+      </c>
+      <c r="AA38">
+        <v>1.44</v>
+      </c>
+      <c r="AB38">
+        <v>2.5</v>
+      </c>
+      <c r="AC38">
+        <v>2.2</v>
+      </c>
+      <c r="AD38">
+        <v>1.69</v>
+      </c>
+      <c r="AE38">
         <v>1.25</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>1.07</v>
-      </c>
-      <c r="Z38">
-        <v>7.5</v>
-      </c>
-      <c r="AA38">
-        <v>1.33</v>
-      </c>
-      <c r="AB38">
-        <v>3.4</v>
-      </c>
-      <c r="AC38">
-        <v>1.81</v>
-      </c>
-      <c r="AD38">
-        <v>1.86</v>
-      </c>
-      <c r="AE38">
-        <v>1.42</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P39">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U39">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="O40">
+        <v>3.65</v>
+      </c>
+      <c r="P40">
+        <v>3.25</v>
+      </c>
+      <c r="Q40">
+        <v>2.35</v>
+      </c>
+      <c r="R40">
+        <v>2.37</v>
+      </c>
+      <c r="S40">
+        <v>1.22</v>
+      </c>
+      <c r="T40">
         <v>3.8</v>
       </c>
-      <c r="P40">
-        <v>4</v>
-      </c>
-      <c r="Q40">
-        <v>2.1</v>
-      </c>
-      <c r="R40">
-        <v>2.35</v>
-      </c>
-      <c r="S40">
-        <v>1.25</v>
-      </c>
-      <c r="T40">
-        <v>3.55</v>
-      </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6865,28 +6865,28 @@
         <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA40">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB40">
+        <v>2.35</v>
+      </c>
+      <c r="AC40">
         <v>2.3</v>
-      </c>
-      <c r="AC40">
-        <v>2.25</v>
       </c>
       <c r="AD40">
         <v>1.55</v>
       </c>
       <c r="AE40">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.54</v>
+        <v>2.29</v>
       </c>
       <c r="O37">
-        <v>4.88</v>
+        <v>3.78</v>
       </c>
       <c r="P37">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="V37">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
+        <v>1.15</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.13</v>
+      </c>
+      <c r="Z37">
+        <v>6</v>
+      </c>
+      <c r="AA37">
+        <v>1.44</v>
+      </c>
+      <c r="AB37">
+        <v>2.5</v>
+      </c>
+      <c r="AC37">
+        <v>2.2</v>
+      </c>
+      <c r="AD37">
+        <v>1.69</v>
+      </c>
+      <c r="AE37">
         <v>1.25</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>1.07</v>
-      </c>
-      <c r="Z37">
-        <v>7.5</v>
-      </c>
-      <c r="AA37">
-        <v>1.33</v>
-      </c>
-      <c r="AB37">
-        <v>3.4</v>
-      </c>
-      <c r="AC37">
-        <v>1.81</v>
-      </c>
-      <c r="AD37">
-        <v>1.86</v>
-      </c>
-      <c r="AE37">
-        <v>1.42</v>
       </c>
       <c r="AF37">
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.29</v>
+        <v>1.71</v>
       </c>
       <c r="O38">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P38">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U38">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD38">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="O39">
+        <v>3.65</v>
+      </c>
+      <c r="P39">
+        <v>3.25</v>
+      </c>
+      <c r="Q39">
+        <v>2.35</v>
+      </c>
+      <c r="R39">
+        <v>2.37</v>
+      </c>
+      <c r="S39">
+        <v>1.22</v>
+      </c>
+      <c r="T39">
         <v>3.8</v>
       </c>
-      <c r="P39">
-        <v>4</v>
-      </c>
-      <c r="Q39">
-        <v>2.1</v>
-      </c>
-      <c r="R39">
-        <v>2.35</v>
-      </c>
-      <c r="S39">
-        <v>1.25</v>
-      </c>
-      <c r="T39">
-        <v>3.55</v>
-      </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6702,28 +6702,28 @@
         <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
+        <v>2.35</v>
+      </c>
+      <c r="AC39">
         <v>2.3</v>
-      </c>
-      <c r="AC39">
-        <v>2.25</v>
       </c>
       <c r="AD39">
         <v>1.55</v>
       </c>
       <c r="AE39">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="O40">
-        <v>3.65</v>
+        <v>4.88</v>
       </c>
       <c r="P40">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="R40">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="V40">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB40">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AC40">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AD40">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AE40">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AF40">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -3409,10 +3409,10 @@
         <v>1.89</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
         <v>2.25</v>
@@ -3445,7 +3445,7 @@
         <v>3.95</v>
       </c>
       <c r="AA19">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
         <v>1.99</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="O20">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="Q20">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R20">
         <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W20">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -3605,25 +3605,25 @@
         <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>6.41</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AC20">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD20">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE20">
+        <v>1.38</v>
+      </c>
+      <c r="AF20">
         <v>1.36</v>
-      </c>
-      <c r="AF20">
-        <v>1.4</v>
       </c>
       <c r="AG20">
         <v>2.88</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,61 +3735,61 @@
         <v>1.91</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
         <v>2.43</v>
       </c>
       <c r="R21">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="V21">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA21">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB21">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD21">
         <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB22">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC22">
         <v>1.63</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O23">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="U23">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="V23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W23">
         <v>1.15</v>
@@ -4094,16 +4094,16 @@
         <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>5.62</v>
+        <v>6.1</v>
       </c>
       <c r="AA23">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB23">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="AC23">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AD23">
         <v>1.63</v>
@@ -4112,10 +4112,10 @@
         <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG23">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>4.12</v>
+        <v>3.84</v>
       </c>
       <c r="Q26">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA26">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AB26">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AC26">
         <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>1.99</v>
+        <v>3.57</v>
       </c>
       <c r="Q30">
-        <v>3.75</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U30">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AC30">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4.32</v>
+        <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>2.27</v>
+        <v>3.75</v>
       </c>
       <c r="R31">
         <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="U31">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.17</v>
+      </c>
+      <c r="Z31">
+        <v>5.4</v>
+      </c>
+      <c r="AA31">
+        <v>1.5</v>
+      </c>
+      <c r="AB31">
+        <v>2.36</v>
+      </c>
+      <c r="AC31">
+        <v>2.35</v>
+      </c>
+      <c r="AD31">
+        <v>1.58</v>
+      </c>
+      <c r="AE31">
+        <v>1.21</v>
+      </c>
+      <c r="AF31">
+        <v>1.47</v>
+      </c>
+      <c r="AG31">
+        <v>2.63</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.22</v>
       </c>
-      <c r="Z31">
-        <v>3.97</v>
-      </c>
-      <c r="AA31">
-        <v>1.75</v>
-      </c>
-      <c r="AB31">
-        <v>1.96</v>
-      </c>
-      <c r="AC31">
-        <v>2.8</v>
-      </c>
-      <c r="AD31">
-        <v>1.4</v>
-      </c>
-      <c r="AE31">
-        <v>1.14</v>
-      </c>
-      <c r="AF31">
-        <v>1.67</v>
-      </c>
-      <c r="AG31">
-        <v>2.05</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.2</v>
-      </c>
       <c r="AK31">
-        <v>2.06</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.6</v>
+        <v>1.46</v>
       </c>
       <c r="O32">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
       <c r="P32">
-        <v>1.99</v>
+        <v>6.15</v>
       </c>
       <c r="Q32">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>5.17</v>
+        <v>4.75</v>
       </c>
       <c r="AA32">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AC32">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AD32">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AE32">
         <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.08</v>
+      </c>
+      <c r="AK32">
         <v>2.55</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.19</v>
-      </c>
-      <c r="AK32">
-        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>4.48</v>
       </c>
       <c r="Q33">
-        <v>1.93</v>
+        <v>2.49</v>
       </c>
       <c r="R33">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="U33">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AB33">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>2.55</v>
+        <v>3.64</v>
       </c>
       <c r="AD33">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="O34">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="P34">
-        <v>4.48</v>
+        <v>5.4</v>
       </c>
       <c r="Q34">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="S34">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="T34">
-        <v>2.84</v>
+        <v>3.58</v>
       </c>
       <c r="U34">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="Z34">
-        <v>3.08</v>
+        <v>4.95</v>
       </c>
       <c r="AA34">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>1.78</v>
+        <v>2.47</v>
       </c>
       <c r="AC34">
-        <v>3.64</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK34">
-        <v>2.04</v>
+        <v>2.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-07-22 21:30:00</t>
+          <t>2026-07-22 22:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>3.45</v>
       </c>
       <c r="R35">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U35">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
         <v>1.11</v>
@@ -6047,28 +6047,28 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
+        <v>1.62</v>
+      </c>
+      <c r="AB35">
+        <v>2.28</v>
+      </c>
+      <c r="AC35">
+        <v>2.6</v>
+      </c>
+      <c r="AD35">
         <v>1.47</v>
       </c>
-      <c r="AB35">
-        <v>2.47</v>
-      </c>
-      <c r="AC35">
-        <v>2.3</v>
-      </c>
-      <c r="AD35">
-        <v>1.6</v>
-      </c>
       <c r="AE35">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG35">
         <v>2.25</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>2.47</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-07-22 22:00:00</t>
+          <t>2026-07-22 22:30:00</t>
         </is>
       </c>
     </row>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
+        <v>1.18</v>
+      </c>
+      <c r="T36">
+        <v>4.33</v>
+      </c>
+      <c r="U36">
+        <v>2.12</v>
+      </c>
+      <c r="V36">
+        <v>1.73</v>
+      </c>
+      <c r="W36">
         <v>1.2</v>
       </c>
-      <c r="T36">
-        <v>3.94</v>
-      </c>
-      <c r="U36">
-        <v>2.04</v>
-      </c>
-      <c r="V36">
-        <v>1.67</v>
-      </c>
-      <c r="W36">
-        <v>1.16</v>
-      </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB36">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC36">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD36">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE36">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
         <v>1.33</v>
       </c>
       <c r="AG36">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="O37">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC37">
         <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE37">
         <v>1.25</v>
       </c>
       <c r="AF37">
+        <v>1.41</v>
+      </c>
+      <c r="AG37">
+        <v>2.68</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.4</v>
       </c>
-      <c r="AG37">
-        <v>2.75</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.26</v>
-      </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,61 +6503,61 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O38">
         <v>3.8</v>
       </c>
       <c r="P38">
+        <v>3.85</v>
+      </c>
+      <c r="Q38">
+        <v>2.19</v>
+      </c>
+      <c r="R38">
+        <v>2.65</v>
+      </c>
+      <c r="S38">
+        <v>1.2</v>
+      </c>
+      <c r="T38">
         <v>4</v>
       </c>
-      <c r="Q38">
-        <v>2.1</v>
-      </c>
-      <c r="R38">
-        <v>2.35</v>
-      </c>
-      <c r="S38">
-        <v>1.25</v>
-      </c>
-      <c r="T38">
-        <v>3.55</v>
-      </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA38">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD38">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
         <v>2.45</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
         <v>2.05</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
         <v>3.25</v>
       </c>
       <c r="Q39">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R39">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="AA39">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC39">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD39">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG39">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
         <v>1.8</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O40">
-        <v>4.88</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
         <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="R40">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S40">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T40">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U40">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V40">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z40">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA40">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB40">
         <v>3.4</v>
       </c>
       <c r="AC40">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD40">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE40">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -612,66 +612,66 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
         <v>1.8</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
         <v>3.9</v>
       </c>
       <c r="Q2">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T2">
         <v>2.67</v>
       </c>
       <c r="U2">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="V2">
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
         <v>2.25</v>
@@ -680,62 +680,62 @@
         <v>1.61</v>
       </c>
       <c r="AC2">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG2">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "69", "88"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,111 +794,111 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q3">
-        <v>4.21</v>
+        <v>4.4</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
         <v>1.82</v>
       </c>
       <c r="AG3">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,130 +938,130 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="O4">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U4">
         <v>3.4</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
         <v>1.45</v>
       </c>
       <c r="Z4">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AA4">
         <v>2.35</v>
       </c>
       <c r="AB4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "70"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "51", "60"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK4">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P15">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q15">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
-        <v>3.62</v>
+        <v>3.78</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AK15">
         <v>1.21</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="O27">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="P27">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA27">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>7.1</v>
+        <v>7.25</v>
       </c>
       <c r="O28">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P28">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O29">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="R29">
         <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
         <v>1.68</v>
       </c>
       <c r="AC29">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
         <v>1.91</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q35">
-        <v>3.45</v>
+        <v>2.48</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="S35">
+        <v>1.18</v>
+      </c>
+      <c r="T35">
+        <v>4.33</v>
+      </c>
+      <c r="U35">
+        <v>2.12</v>
+      </c>
+      <c r="V35">
+        <v>1.73</v>
+      </c>
+      <c r="W35">
+        <v>1.2</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>1.11</v>
+      </c>
+      <c r="Z35">
+        <v>6</v>
+      </c>
+      <c r="AA35">
+        <v>1.42</v>
+      </c>
+      <c r="AB35">
+        <v>3</v>
+      </c>
+      <c r="AC35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>1.76</v>
+      </c>
+      <c r="AE35">
         <v>1.3</v>
       </c>
-      <c r="T35">
-        <v>3.4</v>
-      </c>
-      <c r="U35">
-        <v>2.4</v>
-      </c>
-      <c r="V35">
-        <v>1.52</v>
-      </c>
-      <c r="W35">
-        <v>1.11</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.2</v>
-      </c>
-      <c r="Z35">
-        <v>4.5</v>
-      </c>
-      <c r="AA35">
-        <v>1.62</v>
-      </c>
-      <c r="AB35">
-        <v>2.28</v>
-      </c>
-      <c r="AC35">
-        <v>2.6</v>
-      </c>
-      <c r="AD35">
-        <v>1.47</v>
-      </c>
-      <c r="AE35">
-        <v>1.15</v>
-      </c>
       <c r="AF35">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="W36">
+        <v>1.11</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
         <v>1.2</v>
       </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>1.11</v>
-      </c>
       <c r="Z36">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="AC36">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
+        <v>1.53</v>
+      </c>
+      <c r="AG36">
+        <v>2.25</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.22</v>
+      </c>
+      <c r="AK36">
         <v>1.33</v>
-      </c>
-      <c r="AG36">
-        <v>2.88</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.3</v>
-      </c>
-      <c r="AK36">
-        <v>1.8</v>
       </c>
       <c r="AL36">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.68</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB5">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O6">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="P6">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA6">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AB6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.85</v>
+        <v>5.25</v>
       </c>
       <c r="O7">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA7">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB7">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P8">
-        <v>4.51</v>
+        <v>4.74</v>
       </c>
       <c r="Q8">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U8">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="V8">
         <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="AA8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O11">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="P11">
-        <v>3.22</v>
+        <v>3.62</v>
       </c>
       <c r="Q11">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T11">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="V11">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O12">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA12">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
         <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
+        <v>1.85</v>
+      </c>
+      <c r="AG12">
+        <v>1.92</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.82</v>
       </c>
-      <c r="AG12">
-        <v>1.87</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.7</v>
-      </c>
       <c r="AK12">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P13">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="R13">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="S13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T13">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U13">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V13">
         <v>1.23</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y13">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z13">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AA13">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AB13">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC13">
-        <v>4.55</v>
+        <v>5.69</v>
       </c>
       <c r="AD13">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
         <v>1.62</v>
@@ -2594,62 +2594,62 @@
         <v>1.17</v>
       </c>
       <c r="O14">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Q14">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R14">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
         <v>3.21</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC14">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
+        <v>1.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.18</v>
+      </c>
+      <c r="AF14">
+        <v>2.2</v>
+      </c>
+      <c r="AG14">
         <v>1.53</v>
       </c>
-      <c r="AE14">
-        <v>1.19</v>
-      </c>
-      <c r="AF14">
-        <v>2.25</v>
-      </c>
-      <c r="AG14">
-        <v>1.52</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2920,52 +2920,52 @@
         <v>1.33</v>
       </c>
       <c r="O16">
-        <v>3.91</v>
+        <v>4.7</v>
       </c>
       <c r="P16">
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
+        <v>1.35</v>
+      </c>
+      <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
+        <v>2.86</v>
+      </c>
+      <c r="V16">
+        <v>1.42</v>
+      </c>
+      <c r="W16">
+        <v>1.08</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.29</v>
+      </c>
+      <c r="Z16">
+        <v>3.5</v>
+      </c>
+      <c r="AA16">
+        <v>1.83</v>
+      </c>
+      <c r="AB16">
+        <v>1.93</v>
+      </c>
+      <c r="AC16">
+        <v>3.25</v>
+      </c>
+      <c r="AD16">
         <v>1.33</v>
-      </c>
-      <c r="T16">
-        <v>2.66</v>
-      </c>
-      <c r="U16">
-        <v>2.77</v>
-      </c>
-      <c r="V16">
-        <v>1.38</v>
-      </c>
-      <c r="W16">
-        <v>1.05</v>
-      </c>
-      <c r="X16">
-        <v>1.05</v>
-      </c>
-      <c r="Y16">
-        <v>1.3</v>
-      </c>
-      <c r="Z16">
-        <v>3.14</v>
-      </c>
-      <c r="AA16">
-        <v>1.99</v>
-      </c>
-      <c r="AB16">
-        <v>1.83</v>
-      </c>
-      <c r="AC16">
-        <v>3.4</v>
-      </c>
-      <c r="AD16">
-        <v>1.28</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -2974,7 +2974,7 @@
         <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O17">
         <v>3.15</v>
       </c>
       <c r="P17">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T17">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
-        <v>3.19</v>
+        <v>3.38</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z17">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4224,58 +4224,58 @@
         <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P24">
         <v>2.78</v>
       </c>
       <c r="Q24">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB24">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
         <v>4.1</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG24">
         <v>1.83</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.15</v>
+        <v>4.43</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>5.61</v>
+        <v>5.3</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
+        <v>1.49</v>
+      </c>
+      <c r="T25">
+        <v>2.63</v>
+      </c>
+      <c r="U25">
+        <v>3.38</v>
+      </c>
+      <c r="V25">
+        <v>1.25</v>
+      </c>
+      <c r="W25">
+        <v>1.02</v>
+      </c>
+      <c r="X25">
+        <v>1.1</v>
+      </c>
+      <c r="Y25">
         <v>1.48</v>
       </c>
-      <c r="T25">
-        <v>2.55</v>
-      </c>
-      <c r="U25">
-        <v>3.25</v>
-      </c>
-      <c r="V25">
-        <v>1.27</v>
-      </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.42</v>
-      </c>
       <c r="Z25">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA25">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>4.33</v>
+        <v>5.89</v>
       </c>
       <c r="AD25">
         <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>7.25</v>
+        <v>2</v>
       </c>
       <c r="O28">
+        <v>3.2</v>
+      </c>
+      <c r="P28">
+        <v>4</v>
+      </c>
+      <c r="Q28">
+        <v>2.69</v>
+      </c>
+      <c r="R28">
+        <v>2.05</v>
+      </c>
+      <c r="S28">
+        <v>1.42</v>
+      </c>
+      <c r="T28">
+        <v>2.44</v>
+      </c>
+      <c r="U28">
+        <v>2.88</v>
+      </c>
+      <c r="V28">
+        <v>1.3</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.36</v>
+      </c>
+      <c r="Z28">
+        <v>3.1</v>
+      </c>
+      <c r="AA28">
+        <v>2.2</v>
+      </c>
+      <c r="AB28">
+        <v>1.68</v>
+      </c>
+      <c r="AC28">
         <v>4.33</v>
       </c>
-      <c r="P28">
-        <v>1.49</v>
-      </c>
-      <c r="Q28">
-        <v>6.25</v>
-      </c>
-      <c r="R28">
-        <v>2.3</v>
-      </c>
-      <c r="S28">
-        <v>1.36</v>
-      </c>
-      <c r="T28">
-        <v>3.14</v>
-      </c>
-      <c r="U28">
-        <v>2.75</v>
-      </c>
-      <c r="V28">
-        <v>1.45</v>
-      </c>
-      <c r="W28">
-        <v>1.07</v>
-      </c>
-      <c r="X28">
-        <v>1.03</v>
-      </c>
-      <c r="Y28">
-        <v>1.21</v>
-      </c>
-      <c r="Z28">
-        <v>3.62</v>
-      </c>
-      <c r="AA28">
-        <v>1.85</v>
-      </c>
-      <c r="AB28">
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
+        <v>1.04</v>
+      </c>
+      <c r="AF28">
         <v>1.91</v>
       </c>
-      <c r="AC28">
-        <v>3.13</v>
-      </c>
-      <c r="AD28">
-        <v>1.33</v>
-      </c>
-      <c r="AE28">
-        <v>1.13</v>
-      </c>
-      <c r="AF28">
-        <v>2</v>
-      </c>
       <c r="AG28">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
+        <v>7.25</v>
+      </c>
+      <c r="O29">
+        <v>4.33</v>
+      </c>
+      <c r="P29">
+        <v>1.49</v>
+      </c>
+      <c r="Q29">
+        <v>6.25</v>
+      </c>
+      <c r="R29">
+        <v>2.3</v>
+      </c>
+      <c r="S29">
+        <v>1.36</v>
+      </c>
+      <c r="T29">
+        <v>3.14</v>
+      </c>
+      <c r="U29">
+        <v>2.75</v>
+      </c>
+      <c r="V29">
+        <v>1.45</v>
+      </c>
+      <c r="W29">
+        <v>1.07</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.21</v>
+      </c>
+      <c r="Z29">
+        <v>3.62</v>
+      </c>
+      <c r="AA29">
+        <v>1.85</v>
+      </c>
+      <c r="AB29">
+        <v>1.91</v>
+      </c>
+      <c r="AC29">
+        <v>3.13</v>
+      </c>
+      <c r="AD29">
+        <v>1.33</v>
+      </c>
+      <c r="AE29">
+        <v>1.13</v>
+      </c>
+      <c r="AF29">
         <v>2</v>
       </c>
-      <c r="O29">
-        <v>3.2</v>
-      </c>
-      <c r="P29">
-        <v>4</v>
-      </c>
-      <c r="Q29">
-        <v>2.69</v>
-      </c>
-      <c r="R29">
-        <v>2.05</v>
-      </c>
-      <c r="S29">
-        <v>1.42</v>
-      </c>
-      <c r="T29">
-        <v>2.44</v>
-      </c>
-      <c r="U29">
-        <v>2.88</v>
-      </c>
-      <c r="V29">
-        <v>1.3</v>
-      </c>
-      <c r="W29">
-        <v>1.04</v>
-      </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.36</v>
-      </c>
-      <c r="Z29">
-        <v>3.1</v>
-      </c>
-      <c r="AA29">
-        <v>2.2</v>
-      </c>
-      <c r="AB29">
-        <v>1.68</v>
-      </c>
-      <c r="AC29">
-        <v>4.33</v>
-      </c>
-      <c r="AD29">
+      <c r="AG29">
+        <v>1.8</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.22</v>
       </c>
-      <c r="AE29">
-        <v>1.04</v>
-      </c>
-      <c r="AF29">
-        <v>1.91</v>
-      </c>
-      <c r="AG29">
-        <v>1.77</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.3</v>
-      </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O33">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="Q33">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="U33">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
         <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
         <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1113,14 +1113,14 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "55", "59", "74"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "53", "80"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68", "72", "89"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,130 +1753,130 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="O9">
+        <v>3.7</v>
+      </c>
+      <c r="P9">
+        <v>2.1</v>
+      </c>
+      <c r="Q9">
         <v>3.5</v>
       </c>
-      <c r="P9">
-        <v>2.16</v>
-      </c>
-      <c r="Q9">
-        <v>3.48</v>
-      </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S9">
+        <v>1.25</v>
+      </c>
+      <c r="T9">
+        <v>3.42</v>
+      </c>
+      <c r="U9">
+        <v>2.33</v>
+      </c>
+      <c r="V9">
+        <v>1.62</v>
+      </c>
+      <c r="W9">
+        <v>1.14</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.11</v>
+      </c>
+      <c r="Z9">
+        <v>5.5</v>
+      </c>
+      <c r="AA9">
+        <v>1.47</v>
+      </c>
+      <c r="AB9">
+        <v>2.38</v>
+      </c>
+      <c r="AC9">
+        <v>2.25</v>
+      </c>
+      <c r="AD9">
+        <v>1.5</v>
+      </c>
+      <c r="AE9">
         <v>1.22</v>
       </c>
-      <c r="T9">
-        <v>3.8</v>
-      </c>
-      <c r="U9">
-        <v>2.28</v>
-      </c>
-      <c r="V9">
-        <v>1.6</v>
-      </c>
-      <c r="W9">
-        <v>1.13</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.13</v>
-      </c>
-      <c r="Z9">
-        <v>4.6</v>
-      </c>
-      <c r="AA9">
-        <v>1.53</v>
-      </c>
-      <c r="AB9">
-        <v>2.4</v>
-      </c>
-      <c r="AC9">
-        <v>2.36</v>
-      </c>
-      <c r="AD9">
-        <v>1.6</v>
-      </c>
-      <c r="AE9">
-        <v>1.19</v>
-      </c>
       <c r="AF9">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG9">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "55"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,130 +1916,130 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="O10">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="P10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q10">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="R10">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="S10">
         <v>1.11</v>
       </c>
       <c r="T10">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="U10">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V10">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="W10">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA10">
+        <v>1.22</v>
+      </c>
+      <c r="AB10">
+        <v>4.2</v>
+      </c>
+      <c r="AC10">
+        <v>1.54</v>
+      </c>
+      <c r="AD10">
+        <v>2.27</v>
+      </c>
+      <c r="AE10">
+        <v>1.64</v>
+      </c>
+      <c r="AF10">
+        <v>1.94</v>
+      </c>
+      <c r="AG10">
+        <v>1.71</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>["24", "50", "75"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.03</v>
+      </c>
+      <c r="AK10">
         <v>8.5</v>
       </c>
-      <c r="AA10">
-        <v>1.25</v>
-      </c>
-      <c r="AB10">
-        <v>4</v>
-      </c>
-      <c r="AC10">
-        <v>1.66</v>
-      </c>
-      <c r="AD10">
-        <v>2.1</v>
-      </c>
-      <c r="AE10">
-        <v>1.5</v>
-      </c>
-      <c r="AF10">
-        <v>1.9</v>
-      </c>
-      <c r="AG10">
-        <v>1.83</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.01</v>
-      </c>
-      <c r="AK10">
-        <v>6.75</v>
-      </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O15">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P15">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="Q15">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="U15">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
-        <v>3.78</v>
+        <v>4.47</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG15">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AK15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="P18">
+        <v>3.35</v>
+      </c>
+      <c r="Q18">
+        <v>2.23</v>
+      </c>
+      <c r="R18">
+        <v>2.54</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
         <v>3.5</v>
       </c>
-      <c r="Q18">
-        <v>2.36</v>
-      </c>
-      <c r="R18">
-        <v>2.25</v>
-      </c>
-      <c r="S18">
-        <v>1.29</v>
-      </c>
-      <c r="T18">
-        <v>3.25</v>
-      </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>1.89</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="Q19">
         <v>2.25</v>
@@ -3445,10 +3445,10 @@
         <v>3.95</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
         <v>2.88</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q20">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
         <v>1.2</v>
@@ -3602,31 +3602,31 @@
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
         <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AC20">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AD20">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
         <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,46 +3732,46 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O21">
         <v>3.55</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="Q21">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="R21">
         <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="V21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
         <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
         <v>2</v>
@@ -3780,16 +3780,16 @@
         <v>2.88</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="P22">
-        <v>2.88</v>
+        <v>4.36</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="AA22">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AC22">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AD22">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.65</v>
+        <v>2.31</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="R23">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T23">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="U23">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="V23">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA23">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB23">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="AC23">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="AD23">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AE23">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF23">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AK23">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>3.84</v>
+        <v>3.05</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
         <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
         <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB26">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD26">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE26">
         <v>1.13</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,10 +4719,10 @@
         <v>2.96</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.42</v>
@@ -4731,7 +4731,7 @@
         <v>2.65</v>
       </c>
       <c r="U27">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
         <v>1.38</v>
@@ -4740,34 +4740,34 @@
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
         <v>3.05</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE27">
         <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG27">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O28">
         <v>3.2</v>
@@ -4882,55 +4882,55 @@
         <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="R28">
         <v>2.05</v>
       </c>
       <c r="S28">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T28">
         <v>2.44</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="AA28">
         <v>2.2</v>
       </c>
       <c r="AB28">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD28">
         <v>1.22</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG28">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>7.25</v>
+        <v>7.8</v>
       </c>
       <c r="O29">
         <v>4.33</v>
@@ -5051,16 +5051,16 @@
         <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T29">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V29">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5069,22 +5069,22 @@
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="AA29">
         <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
         <v>1.13</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>2.7</v>
       </c>
       <c r="AK29">
         <v>1.1</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="P30">
-        <v>3.57</v>
+        <v>4.45</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S30">
         <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
         <v>2.45</v>
@@ -5229,22 +5229,22 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
         <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
         <v>2.03</v>
       </c>
       <c r="AC30">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
         <v>1.36</v>
@@ -5256,7 +5256,7 @@
         <v>1.67</v>
       </c>
       <c r="AG30">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P31">
-        <v>1.91</v>
+        <v>5.98</v>
       </c>
       <c r="Q31">
-        <v>3.75</v>
+        <v>1.96</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
         <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U31">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA31">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE31">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK31">
-        <v>1.29</v>
+        <v>2.54</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.46</v>
+        <v>3.25</v>
       </c>
       <c r="O32">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>6.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q32">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T32">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB32">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC32">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AD32">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE32">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="O34">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="P34">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R34">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD34">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.13</v>
       </c>
       <c r="AK34">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="P35">
-        <v>2.77</v>
+        <v>3.52</v>
       </c>
       <c r="Q35">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
         <v>2.62</v>
       </c>
       <c r="S35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U35">
         <v>2.12</v>
       </c>
       <c r="V35">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W35">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
         <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AC35">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD35">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AE35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF35">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG35">
         <v>2.88</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V36">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6213,28 +6213,28 @@
         <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB36">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK36">
         <v>1.33</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.39</v>
+        <v>1.68</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>2.6</v>
+        <v>3.68</v>
       </c>
       <c r="Q37">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="R37">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S37">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="AA37">
+        <v>1.53</v>
+      </c>
+      <c r="AB37">
+        <v>2.5</v>
+      </c>
+      <c r="AC37">
+        <v>2.26</v>
+      </c>
+      <c r="AD37">
+        <v>1.62</v>
+      </c>
+      <c r="AE37">
+        <v>1.22</v>
+      </c>
+      <c r="AF37">
         <v>1.5</v>
       </c>
-      <c r="AB37">
-        <v>2.71</v>
-      </c>
-      <c r="AC37">
-        <v>2.2</v>
-      </c>
-      <c r="AD37">
-        <v>1.71</v>
-      </c>
-      <c r="AE37">
-        <v>1.25</v>
-      </c>
-      <c r="AF37">
-        <v>1.41</v>
-      </c>
       <c r="AG37">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="O38">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P38">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="R38">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U38">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V38">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA38">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="AD38">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG38">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P39">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q39">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T39">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="U39">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>5.17</v>
+        <v>7.5</v>
       </c>
       <c r="AA39">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AB39">
-        <v>2.29</v>
+        <v>3.35</v>
       </c>
       <c r="AC39">
-        <v>2.39</v>
+        <v>1.89</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AE39">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.5</v>
+        <v>2.31</v>
       </c>
       <c r="O40">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q40">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="S40">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="W40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AA40">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AB40">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC40">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AD40">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AK40">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-07-22.xlsx
+++ b/jogos_2026-07-22.xlsx
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "58", "78"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "54", "66"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,16 +2344,16 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "79", "82"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2591,55 +2591,55 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="O14">
-        <v>5.75</v>
+        <v>6.6</v>
       </c>
       <c r="P14">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="Q14">
         <v>1.56</v>
       </c>
       <c r="R14">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="S14">
         <v>1.27</v>
       </c>
       <c r="T14">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB14">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE14">
         <v>1.18</v>
@@ -2648,7 +2648,7 @@
         <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK14">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O16">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
         <v>1.35</v>
@@ -2938,28 +2938,28 @@
         <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA16">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC16">
         <v>3.25</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,52 +3080,52 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T17">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="U17">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="V17">
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA17">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC17">
-        <v>4.2</v>
+        <v>4.41</v>
       </c>
       <c r="AD17">
         <v>1.2</v>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4221,22 +4221,22 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O24">
         <v>3.03</v>
       </c>
       <c r="P24">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q24">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="R24">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
         <v>2.7</v>
@@ -4248,28 +4248,28 @@
         <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="Z24">
         <v>2.9</v>
       </c>
       <c r="AA24">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AB24">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC24">
         <v>4.1</v>
       </c>
       <c r="AD24">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
         <v>1.02</v>
@@ -4278,7 +4278,7 @@
         <v>1.77</v>
       </c>
       <c r="AG24">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,55 +4384,55 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.43</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q25">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S25">
         <v>1.49</v>
       </c>
       <c r="T25">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
         <v>3.38</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
         <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AA25">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AB25">
         <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>5.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
         <v>1.05</v>
@@ -4441,7 +4441,7 @@
         <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="AK25">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5691,28 +5691,28 @@
         <v>1.8</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="P33">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
         <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
         <v>2.8</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5727,19 +5727,19 @@
         <v>3.3</v>
       </c>
       <c r="AA33">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB33">
         <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.85</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q39">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S39">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="V39">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="W39">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA39">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AB39">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AC39">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="AD39">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
         <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AK39">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="R40">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="V40">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB40">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AC40">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
         <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AK40">
-        <v>1.59</v>
+        <v>2.38</v>
       </c>
       <c r="AL40">
         <v>0</v>
